--- a/Sales_Xbox_Gamepass.xlsx
+++ b/Sales_Xbox_Gamepass.xlsx
@@ -2,27 +2,38 @@
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
   <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29530"/>
-  <workbookPr defaultThemeVersion="202300"/>
+  <workbookPr hidePivotFieldList="1" defaultThemeVersion="202300"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://petrobrasbr-my.sharepoint.com/personal/hugo_knupp_prestserv_petrobras_com_br/Documents/Projetos/20. Dash Excel/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="87" documentId="8_{D02754C7-DAC9-4305-876D-C5DBD1EB8399}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{187A7224-0AB4-4E1C-9EDA-66572DBFAEE6}"/>
+  <xr:revisionPtr revIDLastSave="184" documentId="8_{D02754C7-DAC9-4305-876D-C5DBD1EB8399}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{1EF852B7-FC3C-4734-B593-2F4291074E24}"/>
   <bookViews>
-    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" activeTab="3" xr2:uid="{28DD5B76-0634-4F87-BE60-8BFA7EF2E23B}"/>
+    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" tabRatio="0" firstSheet="3" activeTab="3" xr2:uid="{28DD5B76-0634-4F87-BE60-8BFA7EF2E23B}"/>
   </bookViews>
   <sheets>
-    <sheet name="A̳ssets" sheetId="1" r:id="rId1"/>
-    <sheet name="B̳ases" sheetId="2" r:id="rId2"/>
-    <sheet name="C̳álculos" sheetId="3" r:id="rId3"/>
+    <sheet name="A̳ssets" sheetId="1" state="hidden" r:id="rId1"/>
+    <sheet name="B̳ases" sheetId="2" state="hidden" r:id="rId2"/>
+    <sheet name="C̳álculos" sheetId="3" state="hidden" r:id="rId3"/>
     <sheet name="D̳ashboard" sheetId="4" r:id="rId4"/>
   </sheets>
+  <definedNames>
+    <definedName name="SegmentaçãodeDados_Subscription_Type">#N/A</definedName>
+  </definedNames>
   <calcPr calcId="191029"/>
   <pivotCaches>
-    <pivotCache cacheId="4" r:id="rId5"/>
+    <pivotCache cacheId="0" r:id="rId5"/>
   </pivotCaches>
   <extLst>
+    <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{BBE1A952-AA13-448e-AADC-164F8A28A991}">
+      <x14:slicerCaches>
+        <x14:slicerCache r:id="rId6"/>
+      </x14:slicerCaches>
+    </ext>
+    <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{79F54976-1DA5-4618-B147-4CDE4B953A38}">
+      <x14:workbookPr/>
+    </ext>
     <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{140A7094-0E35-4892-8432-C4D2E57EDEB5}">
       <x15:workbookPr chartTrackingRefBase="1"/>
     </ext>
@@ -1005,7 +1016,7 @@
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
-<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
+<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr9="http://schemas.microsoft.com/office/spreadsheetml/2016/revision9" mc:Ignorable="x14ac x16r2 xr xr9">
   <numFmts count="1">
     <numFmt numFmtId="44" formatCode="_-&quot;R$&quot;\ * #,##0.00_-;\-&quot;R$&quot;\ * #,##0.00_-;_-&quot;R$&quot;\ * &quot;-&quot;??_-;_-@_-"/>
   </numFmts>
@@ -1120,7 +1131,7 @@
     <xf numFmtId="0" fontId="1" fillId="0" borderId="1" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0"/>
     <xf numFmtId="44" fontId="2" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="19">
+  <cellXfs count="18">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="1"/>
     <xf numFmtId="0" fontId="0" fillId="2" borderId="0" xfId="0" applyFill="1"/>
@@ -1149,14 +1160,13 @@
     <xf numFmtId="44" fontId="0" fillId="0" borderId="0" xfId="2" applyFont="1"/>
     <xf numFmtId="0" fontId="4" fillId="4" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
     <xf numFmtId="0" fontId="0" fillId="8" borderId="0" xfId="0" applyFill="1"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
   </cellXfs>
   <cellStyles count="3">
     <cellStyle name="Moeda" xfId="2" builtinId="4"/>
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
     <cellStyle name="Título 1" xfId="1" builtinId="16"/>
   </cellStyles>
-  <dxfs count="14">
+  <dxfs count="18">
     <dxf>
       <alignment horizontal="center" vertical="center" textRotation="0" wrapText="1" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
     </dxf>
@@ -1199,25 +1209,605 @@
     <dxf>
       <alignment horizontal="center" vertical="center" textRotation="0" wrapText="1" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
     </dxf>
+    <dxf>
+      <font>
+        <b/>
+        <color theme="1"/>
+      </font>
+      <border>
+        <bottom style="thin">
+          <color theme="4"/>
+        </bottom>
+        <vertical/>
+        <horizontal/>
+      </border>
+    </dxf>
+    <dxf>
+      <font>
+        <color theme="1"/>
+      </font>
+      <fill>
+        <patternFill patternType="solid">
+          <bgColor rgb="FF2AE6B1"/>
+        </patternFill>
+      </fill>
+      <border>
+        <left style="thin">
+          <color rgb="FF2AE6B1"/>
+        </left>
+        <right style="thin">
+          <color rgb="FF2AE6B1"/>
+        </right>
+        <top style="thin">
+          <color rgb="FF2AE6B1"/>
+        </top>
+        <bottom style="thin">
+          <color rgb="FF2AE6B1"/>
+        </bottom>
+        <vertical/>
+        <horizontal/>
+      </border>
+    </dxf>
+    <dxf>
+      <font>
+        <b/>
+        <color theme="1"/>
+      </font>
+      <border>
+        <bottom style="thin">
+          <color theme="4"/>
+        </bottom>
+        <vertical/>
+        <horizontal/>
+      </border>
+    </dxf>
+    <dxf>
+      <font>
+        <color theme="1"/>
+      </font>
+      <fill>
+        <patternFill patternType="solid">
+          <bgColor rgb="FF2AE6B1"/>
+        </patternFill>
+      </fill>
+      <border>
+        <left style="thin">
+          <color rgb="FF2AE6B1"/>
+        </left>
+        <right style="thin">
+          <color rgb="FF2AE6B1"/>
+        </right>
+        <top style="thin">
+          <color rgb="FF2AE6B1"/>
+        </top>
+        <bottom style="thin">
+          <color rgb="FF2AE6B1"/>
+        </bottom>
+        <vertical/>
+        <horizontal/>
+      </border>
+    </dxf>
   </dxfs>
-  <tableStyles count="0" defaultTableStyle="TableStyleMedium2" defaultPivotStyle="PivotStyleLight16"/>
+  <tableStyles count="2" defaultTableStyle="TableStyleMedium2" defaultPivotStyle="PivotStyleLight16">
+    <tableStyle name="SlicerStyleLight1 2" pivot="0" table="0" count="10" xr9:uid="{16BB54E6-943A-45D8-8B53-66E7F7B1C37D}">
+      <tableStyleElement type="wholeTable" dxfId="17"/>
+      <tableStyleElement type="headerRow" dxfId="16"/>
+    </tableStyle>
+    <tableStyle name="SlicerStyleLight1 2 2" pivot="0" table="0" count="10" xr9:uid="{66652A0D-9852-4557-B76C-9BA3EBC91205}">
+      <tableStyleElement type="wholeTable" dxfId="15"/>
+      <tableStyleElement type="headerRow" dxfId="14"/>
+    </tableStyle>
+  </tableStyles>
   <colors>
     <mruColors>
       <color rgb="FF2AE6B1"/>
+      <color rgb="FFFFFFFF"/>
+      <color rgb="FF22C55E"/>
+      <color rgb="FF5BF6A8"/>
       <color rgb="FF9BC848"/>
-      <color rgb="FF22C55E"/>
       <color rgb="FFE70011"/>
       <color rgb="FFE8E6E9"/>
-      <color rgb="FF5BF6A8"/>
       <color rgb="FF000000"/>
       <color rgb="FFE0E0E0"/>
       <color rgb="FFEDEDED"/>
-      <color rgb="FFF7F8FC"/>
     </mruColors>
   </colors>
   <extLst>
+    <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{46F421CA-312F-682f-3DD2-61675219B42D}">
+      <x14:dxfs count="16">
+        <dxf>
+          <font>
+            <color rgb="FF000000"/>
+          </font>
+          <fill>
+            <gradientFill degree="90">
+              <stop position="0">
+                <color rgb="FFF8E162"/>
+              </stop>
+              <stop position="1">
+                <color rgb="FFFCF7E0"/>
+              </stop>
+            </gradientFill>
+          </fill>
+          <border>
+            <left style="thin">
+              <color rgb="FF999999"/>
+            </left>
+            <right style="thin">
+              <color rgb="FF999999"/>
+            </right>
+            <top style="thin">
+              <color rgb="FF999999"/>
+            </top>
+            <bottom style="thin">
+              <color rgb="FF999999"/>
+            </bottom>
+            <vertical/>
+            <horizontal/>
+          </border>
+        </dxf>
+        <dxf>
+          <font>
+            <color rgb="FF000000"/>
+          </font>
+          <fill>
+            <gradientFill degree="90">
+              <stop position="0">
+                <color rgb="FFF8E162"/>
+              </stop>
+              <stop position="1">
+                <color rgb="FFFCF7E0"/>
+              </stop>
+            </gradientFill>
+          </fill>
+          <border>
+            <left style="thin">
+              <color rgb="FF999999"/>
+            </left>
+            <right style="thin">
+              <color rgb="FF999999"/>
+            </right>
+            <top style="thin">
+              <color rgb="FF999999"/>
+            </top>
+            <bottom style="thin">
+              <color rgb="FF999999"/>
+            </bottom>
+            <vertical/>
+            <horizontal/>
+          </border>
+        </dxf>
+        <dxf>
+          <font>
+            <color rgb="FF000000"/>
+          </font>
+          <fill>
+            <gradientFill degree="90">
+              <stop position="0">
+                <color rgb="FFF8E162"/>
+              </stop>
+              <stop position="1">
+                <color rgb="FFFCF7E0"/>
+              </stop>
+            </gradientFill>
+          </fill>
+          <border>
+            <left style="thin">
+              <color rgb="FF999999"/>
+            </left>
+            <right style="thin">
+              <color rgb="FF999999"/>
+            </right>
+            <top style="thin">
+              <color rgb="FF999999"/>
+            </top>
+            <bottom style="thin">
+              <color rgb="FF999999"/>
+            </bottom>
+            <vertical/>
+            <horizontal/>
+          </border>
+        </dxf>
+        <dxf>
+          <font>
+            <color rgb="FF000000"/>
+          </font>
+          <fill>
+            <gradientFill degree="90">
+              <stop position="0">
+                <color rgb="FFF8E162"/>
+              </stop>
+              <stop position="1">
+                <color rgb="FFFCF7E0"/>
+              </stop>
+            </gradientFill>
+          </fill>
+          <border>
+            <left style="thin">
+              <color rgb="FF999999"/>
+            </left>
+            <right style="thin">
+              <color rgb="FF999999"/>
+            </right>
+            <top style="thin">
+              <color rgb="FF999999"/>
+            </top>
+            <bottom style="thin">
+              <color rgb="FF999999"/>
+            </bottom>
+            <vertical/>
+            <horizontal/>
+          </border>
+        </dxf>
+        <dxf>
+          <font>
+            <color rgb="FF828282"/>
+          </font>
+          <fill>
+            <patternFill patternType="solid">
+              <fgColor theme="4" tint="0.79995117038483843"/>
+              <bgColor rgb="FF2AE6B1"/>
+            </patternFill>
+          </fill>
+          <border>
+            <left style="thin">
+              <color rgb="FFCCCCCC"/>
+            </left>
+            <right style="thin">
+              <color rgb="FFCCCCCC"/>
+            </right>
+            <top style="thin">
+              <color rgb="FFCCCCCC"/>
+            </top>
+            <bottom style="thin">
+              <color rgb="FFCCCCCC"/>
+            </bottom>
+            <vertical/>
+            <horizontal/>
+          </border>
+        </dxf>
+        <dxf>
+          <font>
+            <color rgb="FF000000"/>
+          </font>
+          <fill>
+            <patternFill patternType="solid">
+              <fgColor theme="4" tint="0.59999389629810485"/>
+              <bgColor rgb="FF2AE6B1"/>
+            </patternFill>
+          </fill>
+          <border>
+            <left style="thin">
+              <color rgb="FF999999"/>
+            </left>
+            <right style="thin">
+              <color rgb="FF999999"/>
+            </right>
+            <top style="thin">
+              <color rgb="FF999999"/>
+            </top>
+            <bottom style="thin">
+              <color rgb="FF999999"/>
+            </bottom>
+            <vertical/>
+            <horizontal/>
+          </border>
+        </dxf>
+        <dxf>
+          <font>
+            <color rgb="FF828282"/>
+          </font>
+          <fill>
+            <patternFill patternType="solid">
+              <fgColor rgb="FFFFFFFF"/>
+              <bgColor rgb="FFFFFFFF"/>
+            </patternFill>
+          </fill>
+          <border>
+            <left style="thin">
+              <color rgb="FFE0E0E0"/>
+            </left>
+            <right style="thin">
+              <color rgb="FFE0E0E0"/>
+            </right>
+            <top style="thin">
+              <color rgb="FFE0E0E0"/>
+            </top>
+            <bottom style="thin">
+              <color rgb="FFE0E0E0"/>
+            </bottom>
+            <vertical/>
+            <horizontal/>
+          </border>
+        </dxf>
+        <dxf>
+          <font>
+            <color rgb="FF000000"/>
+          </font>
+          <fill>
+            <patternFill patternType="solid">
+              <fgColor rgb="FFFFFFFF"/>
+              <bgColor rgb="FFFFFFFF"/>
+            </patternFill>
+          </fill>
+          <border>
+            <left style="thin">
+              <color rgb="FFCCCCCC"/>
+            </left>
+            <right style="thin">
+              <color rgb="FFCCCCCC"/>
+            </right>
+            <top style="thin">
+              <color rgb="FFCCCCCC"/>
+            </top>
+            <bottom style="thin">
+              <color rgb="FFCCCCCC"/>
+            </bottom>
+            <vertical/>
+            <horizontal/>
+          </border>
+        </dxf>
+        <dxf>
+          <font>
+            <color rgb="FF000000"/>
+          </font>
+          <fill>
+            <gradientFill degree="90">
+              <stop position="0">
+                <color rgb="FFF8E162"/>
+              </stop>
+              <stop position="1">
+                <color rgb="FFFCF7E0"/>
+              </stop>
+            </gradientFill>
+          </fill>
+          <border>
+            <left style="thin">
+              <color rgb="FF999999"/>
+            </left>
+            <right style="thin">
+              <color rgb="FF999999"/>
+            </right>
+            <top style="thin">
+              <color rgb="FF999999"/>
+            </top>
+            <bottom style="thin">
+              <color rgb="FF999999"/>
+            </bottom>
+            <vertical/>
+            <horizontal/>
+          </border>
+        </dxf>
+        <dxf>
+          <font>
+            <color rgb="FF000000"/>
+          </font>
+          <fill>
+            <gradientFill degree="90">
+              <stop position="0">
+                <color rgb="FFF8E162"/>
+              </stop>
+              <stop position="1">
+                <color rgb="FFFCF7E0"/>
+              </stop>
+            </gradientFill>
+          </fill>
+          <border>
+            <left style="thin">
+              <color rgb="FF999999"/>
+            </left>
+            <right style="thin">
+              <color rgb="FF999999"/>
+            </right>
+            <top style="thin">
+              <color rgb="FF999999"/>
+            </top>
+            <bottom style="thin">
+              <color rgb="FF999999"/>
+            </bottom>
+            <vertical/>
+            <horizontal/>
+          </border>
+        </dxf>
+        <dxf>
+          <font>
+            <color rgb="FF000000"/>
+          </font>
+          <fill>
+            <gradientFill degree="90">
+              <stop position="0">
+                <color rgb="FFF8E162"/>
+              </stop>
+              <stop position="1">
+                <color rgb="FFFCF7E0"/>
+              </stop>
+            </gradientFill>
+          </fill>
+          <border>
+            <left style="thin">
+              <color rgb="FF999999"/>
+            </left>
+            <right style="thin">
+              <color rgb="FF999999"/>
+            </right>
+            <top style="thin">
+              <color rgb="FF999999"/>
+            </top>
+            <bottom style="thin">
+              <color rgb="FF999999"/>
+            </bottom>
+            <vertical/>
+            <horizontal/>
+          </border>
+        </dxf>
+        <dxf>
+          <font>
+            <color rgb="FF000000"/>
+          </font>
+          <fill>
+            <gradientFill degree="90">
+              <stop position="0">
+                <color rgb="FFF8E162"/>
+              </stop>
+              <stop position="1">
+                <color rgb="FFFCF7E0"/>
+              </stop>
+            </gradientFill>
+          </fill>
+          <border>
+            <left style="thin">
+              <color rgb="FF999999"/>
+            </left>
+            <right style="thin">
+              <color rgb="FF999999"/>
+            </right>
+            <top style="thin">
+              <color rgb="FF999999"/>
+            </top>
+            <bottom style="thin">
+              <color rgb="FF999999"/>
+            </bottom>
+            <vertical/>
+            <horizontal/>
+          </border>
+        </dxf>
+        <dxf>
+          <font>
+            <color rgb="FF828282"/>
+          </font>
+          <fill>
+            <patternFill patternType="solid">
+              <fgColor theme="4" tint="0.79998168889431442"/>
+              <bgColor theme="4" tint="0.79998168889431442"/>
+            </patternFill>
+          </fill>
+          <border>
+            <left style="thin">
+              <color rgb="FFCCCCCC"/>
+            </left>
+            <right style="thin">
+              <color rgb="FFCCCCCC"/>
+            </right>
+            <top style="thin">
+              <color rgb="FFCCCCCC"/>
+            </top>
+            <bottom style="thin">
+              <color rgb="FFCCCCCC"/>
+            </bottom>
+            <vertical/>
+            <horizontal/>
+          </border>
+        </dxf>
+        <dxf>
+          <font>
+            <color rgb="FF000000"/>
+          </font>
+          <fill>
+            <patternFill patternType="solid">
+              <fgColor theme="4" tint="0.59999389629810485"/>
+              <bgColor rgb="FF22C55E"/>
+            </patternFill>
+          </fill>
+          <border>
+            <left style="thin">
+              <color rgb="FF999999"/>
+            </left>
+            <right style="thin">
+              <color rgb="FF999999"/>
+            </right>
+            <top style="thin">
+              <color rgb="FF999999"/>
+            </top>
+            <bottom style="thin">
+              <color rgb="FF999999"/>
+            </bottom>
+            <vertical/>
+            <horizontal/>
+          </border>
+        </dxf>
+        <dxf>
+          <font>
+            <color rgb="FF828282"/>
+          </font>
+          <fill>
+            <patternFill patternType="solid">
+              <fgColor rgb="FFFFFFFF"/>
+              <bgColor rgb="FFFFFFFF"/>
+            </patternFill>
+          </fill>
+          <border>
+            <left style="thin">
+              <color rgb="FFE0E0E0"/>
+            </left>
+            <right style="thin">
+              <color rgb="FFE0E0E0"/>
+            </right>
+            <top style="thin">
+              <color rgb="FFE0E0E0"/>
+            </top>
+            <bottom style="thin">
+              <color rgb="FFE0E0E0"/>
+            </bottom>
+            <vertical/>
+            <horizontal/>
+          </border>
+        </dxf>
+        <dxf>
+          <font>
+            <color rgb="FF000000"/>
+          </font>
+          <fill>
+            <patternFill patternType="solid">
+              <fgColor rgb="FFFFFFFF"/>
+              <bgColor rgb="FF2AE6B1"/>
+            </patternFill>
+          </fill>
+          <border>
+            <left style="thin">
+              <color rgb="FFCCCCCC"/>
+            </left>
+            <right style="thin">
+              <color rgb="FFCCCCCC"/>
+            </right>
+            <top style="thin">
+              <color rgb="FFCCCCCC"/>
+            </top>
+            <bottom style="thin">
+              <color rgb="FFCCCCCC"/>
+            </bottom>
+            <vertical/>
+            <horizontal/>
+          </border>
+        </dxf>
+      </x14:dxfs>
+    </ext>
     <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{EB79DEF2-80B8-43e5-95BD-54CBDDF9020C}">
-      <x14:slicerStyles defaultSlicerStyle="SlicerStyleLight1"/>
+      <x14:slicerStyles defaultSlicerStyle="SlicerStyleLight1 2">
+        <x14:slicerStyle name="SlicerStyleLight1 2">
+          <x14:slicerStyleElements>
+            <x14:slicerStyleElement type="unselectedItemWithData" dxfId="15"/>
+            <x14:slicerStyleElement type="unselectedItemWithNoData" dxfId="14"/>
+            <x14:slicerStyleElement type="selectedItemWithData" dxfId="13"/>
+            <x14:slicerStyleElement type="selectedItemWithNoData" dxfId="12"/>
+            <x14:slicerStyleElement type="hoveredUnselectedItemWithData" dxfId="11"/>
+            <x14:slicerStyleElement type="hoveredSelectedItemWithData" dxfId="10"/>
+            <x14:slicerStyleElement type="hoveredUnselectedItemWithNoData" dxfId="9"/>
+            <x14:slicerStyleElement type="hoveredSelectedItemWithNoData" dxfId="8"/>
+          </x14:slicerStyleElements>
+        </x14:slicerStyle>
+        <x14:slicerStyle name="SlicerStyleLight1 2 2">
+          <x14:slicerStyleElements>
+            <x14:slicerStyleElement type="unselectedItemWithData" dxfId="7"/>
+            <x14:slicerStyleElement type="unselectedItemWithNoData" dxfId="6"/>
+            <x14:slicerStyleElement type="selectedItemWithData" dxfId="5"/>
+            <x14:slicerStyleElement type="selectedItemWithNoData" dxfId="4"/>
+            <x14:slicerStyleElement type="hoveredUnselectedItemWithData" dxfId="3"/>
+            <x14:slicerStyleElement type="hoveredSelectedItemWithData" dxfId="2"/>
+            <x14:slicerStyleElement type="hoveredUnselectedItemWithNoData" dxfId="1"/>
+            <x14:slicerStyleElement type="hoveredSelectedItemWithNoData" dxfId="0"/>
+          </x14:slicerStyleElements>
+        </x14:slicerStyle>
+      </x14:slicerStyles>
     </ext>
     <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{9260A510-F301-46a8-8635-F512D64BE5F5}">
       <x15:timelineStyles defaultTimelineStyle="TimeSlicerStyleLight1"/>
@@ -2023,13 +2613,13 @@
                 <c:formatCode>_("R$"* #,##0.00_);_("R$"* \(#,##0.00\);_("R$"* "-"??_);_(@_)</c:formatCode>
                 <c:ptCount val="3"/>
                 <c:pt idx="0">
-                  <c:v>444</c:v>
+                  <c:v>192</c:v>
                 </c:pt>
                 <c:pt idx="1">
-                  <c:v>1801</c:v>
+                  <c:v>958</c:v>
                 </c:pt>
                 <c:pt idx="2">
-                  <c:v>5388</c:v>
+                  <c:v>2421</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -2568,7 +3158,9 @@
             <a:effectLst/>
           </c:spPr>
           <c:txPr>
-            <a:bodyPr rot="0" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
+            <a:bodyPr rot="0" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" lIns="38100" tIns="19050" rIns="38100" bIns="19050" anchor="ctr" anchorCtr="1">
+              <a:spAutoFit/>
+            </a:bodyPr>
             <a:lstStyle/>
             <a:p>
               <a:pPr>
@@ -2620,7 +3212,9 @@
             <a:effectLst/>
           </c:spPr>
           <c:txPr>
-            <a:bodyPr rot="0" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
+            <a:bodyPr rot="0" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" lIns="38100" tIns="19050" rIns="38100" bIns="19050" anchor="ctr" anchorCtr="1">
+              <a:spAutoFit/>
+            </a:bodyPr>
             <a:lstStyle/>
             <a:p>
               <a:pPr>
@@ -2742,13 +3336,13 @@
                 <c:formatCode>General</c:formatCode>
                 <c:ptCount val="3"/>
                 <c:pt idx="0">
-                  <c:v>50</c:v>
+                  <c:v>37</c:v>
                 </c:pt>
                 <c:pt idx="1">
-                  <c:v>47</c:v>
+                  <c:v>40</c:v>
                 </c:pt>
                 <c:pt idx="2">
-                  <c:v>50</c:v>
+                  <c:v>34</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -2808,13 +3402,13 @@
                 <c:formatCode>General</c:formatCode>
                 <c:ptCount val="3"/>
                 <c:pt idx="0">
-                  <c:v>51</c:v>
+                  <c:v>12</c:v>
                 </c:pt>
                 <c:pt idx="1">
-                  <c:v>49</c:v>
+                  <c:v>5</c:v>
                 </c:pt>
                 <c:pt idx="2">
-                  <c:v>48</c:v>
+                  <c:v>11</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -4908,7 +5502,7 @@
       </xdr:nvGrpSpPr>
       <xdr:grpSpPr>
         <a:xfrm>
-          <a:off x="1571624" y="1190626"/>
+          <a:off x="2219324" y="1190626"/>
           <a:ext cx="5534026" cy="2943224"/>
           <a:chOff x="3914774" y="1381125"/>
           <a:chExt cx="5534026" cy="3124199"/>
@@ -5101,7 +5695,7 @@
       </xdr:nvGrpSpPr>
       <xdr:grpSpPr>
         <a:xfrm>
-          <a:off x="7553325" y="1199598"/>
+          <a:off x="8201025" y="1199598"/>
           <a:ext cx="5160946" cy="2943224"/>
           <a:chOff x="11324048" y="1278671"/>
           <a:chExt cx="5160946" cy="2943224"/>
@@ -5274,7 +5868,7 @@
       </xdr:nvGrpSpPr>
       <xdr:grpSpPr>
         <a:xfrm>
-          <a:off x="1619250" y="4457700"/>
+          <a:off x="2266950" y="4457700"/>
           <a:ext cx="5486401" cy="1485900"/>
           <a:chOff x="1619250" y="4457700"/>
           <a:chExt cx="5486401" cy="1485900"/>
@@ -5386,7 +5980,7 @@
                 <a:latin typeface="Aptos Narrow"/>
               </a:rPr>
               <a:pPr algn="ctr"/>
-              <a:t> R$ 7.633,00 </a:t>
+              <a:t> R$ 3.571,00 </a:t>
             </a:fld>
             <a:endParaRPr lang="pt-BR" sz="5400">
               <a:solidFill>
@@ -5487,7 +6081,7 @@
       </xdr:nvGrpSpPr>
       <xdr:grpSpPr>
         <a:xfrm>
-          <a:off x="7553326" y="4448175"/>
+          <a:off x="8201026" y="4448175"/>
           <a:ext cx="5160946" cy="1485900"/>
           <a:chOff x="1619250" y="4457700"/>
           <a:chExt cx="5486401" cy="1485900"/>
@@ -5598,7 +6192,8 @@
                 </a:solidFill>
                 <a:latin typeface="Aptos Narrow"/>
               </a:rPr>
-              <a:t> R$ 3.786,00 </a:t>
+              <a:pPr algn="ctr"/>
+              <a:t> R$ 747,00 </a:t>
             </a:fld>
             <a:endParaRPr lang="pt-BR" sz="34400">
               <a:solidFill>
@@ -5673,6 +6268,84 @@
     </xdr:grpSp>
     <xdr:clientData/>
   </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor editAs="oneCell">
+    <xdr:from>
+      <xdr:col>0</xdr:col>
+      <xdr:colOff>0</xdr:colOff>
+      <xdr:row>5</xdr:row>
+      <xdr:rowOff>66675</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>0</xdr:col>
+      <xdr:colOff>2009774</xdr:colOff>
+      <xdr:row>11</xdr:row>
+      <xdr:rowOff>76200</xdr:rowOff>
+    </xdr:to>
+    <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main">
+      <mc:Choice Requires="a14">
+        <xdr:graphicFrame macro="">
+          <xdr:nvGraphicFramePr>
+            <xdr:cNvPr id="9" name="Subscription Type">
+              <a:extLst>
+                <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+                  <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{BC24B343-A5DB-4EBE-9AE6-BAB59318D184}"/>
+                </a:ext>
+              </a:extLst>
+            </xdr:cNvPr>
+            <xdr:cNvGraphicFramePr/>
+          </xdr:nvGraphicFramePr>
+          <xdr:xfrm>
+            <a:off x="0" y="0"/>
+            <a:ext cx="0" cy="0"/>
+          </xdr:xfrm>
+          <a:graphic>
+            <a:graphicData uri="http://schemas.microsoft.com/office/drawing/2010/slicer">
+              <sle:slicer xmlns:sle="http://schemas.microsoft.com/office/drawing/2010/slicer" name="Subscription Type"/>
+            </a:graphicData>
+          </a:graphic>
+        </xdr:graphicFrame>
+      </mc:Choice>
+      <mc:Fallback xmlns="">
+        <xdr:sp macro="" textlink="">
+          <xdr:nvSpPr>
+            <xdr:cNvPr id="0" name=""/>
+            <xdr:cNvSpPr>
+              <a:spLocks noTextEdit="1"/>
+            </xdr:cNvSpPr>
+          </xdr:nvSpPr>
+          <xdr:spPr>
+            <a:xfrm>
+              <a:off x="0" y="1847850"/>
+              <a:ext cx="2009774" cy="1276350"/>
+            </a:xfrm>
+            <a:prstGeom prst="rect">
+              <a:avLst/>
+            </a:prstGeom>
+            <a:solidFill>
+              <a:prstClr val="white"/>
+            </a:solidFill>
+            <a:ln w="1">
+              <a:solidFill>
+                <a:prstClr val="green"/>
+              </a:solidFill>
+            </a:ln>
+          </xdr:spPr>
+          <xdr:txBody>
+            <a:bodyPr vertOverflow="clip" horzOverflow="clip"/>
+            <a:lstStyle/>
+            <a:p>
+              <a:r>
+                <a:rPr lang="pt-BR" sz="1100"/>
+                <a:t>Esta forma representa uma segmentação de dados. Segmentações de dados têm suporte no Excel 2010 ou versões posteriores.
+\Se a forma tiver sido modificada em uma versão anterior do Excel, ou se a pasta de trabalho tiver sido salva no Excel 2003 ou versões anteriores, a segmentação de dados não poderá ser usada.</a:t>
+              </a:r>
+            </a:p>
+          </xdr:txBody>
+        </xdr:sp>
+      </mc:Fallback>
+    </mc:AlternateContent>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
 </xdr:wsDr>
 </file>
 
@@ -5696,7 +6369,302 @@
       </sharedItems>
     </cacheField>
     <cacheField name="Start Date" numFmtId="14">
-      <sharedItems containsSemiMixedTypes="0" containsNonDate="0" containsDate="1" containsString="0" minDate="2024-01-01T00:00:00" maxDate="2024-12-17T00:00:00"/>
+      <sharedItems containsSemiMixedTypes="0" containsNonDate="0" containsDate="1" containsString="0" minDate="2024-01-01T00:00:00" maxDate="2024-12-17T00:00:00" count="294">
+        <d v="2024-01-01T00:00:00"/>
+        <d v="2024-01-15T00:00:00"/>
+        <d v="2024-02-10T00:00:00"/>
+        <d v="2024-02-20T00:00:00"/>
+        <d v="2024-03-05T00:00:00"/>
+        <d v="2024-03-02T00:00:00"/>
+        <d v="2024-03-03T00:00:00"/>
+        <d v="2024-03-04T00:00:00"/>
+        <d v="2024-03-06T00:00:00"/>
+        <d v="2024-03-07T00:00:00"/>
+        <d v="2024-03-08T00:00:00"/>
+        <d v="2024-03-09T00:00:00"/>
+        <d v="2024-03-10T00:00:00"/>
+        <d v="2024-03-11T00:00:00"/>
+        <d v="2024-03-12T00:00:00"/>
+        <d v="2024-03-13T00:00:00"/>
+        <d v="2024-03-14T00:00:00"/>
+        <d v="2024-03-15T00:00:00"/>
+        <d v="2024-03-16T00:00:00"/>
+        <d v="2024-03-17T00:00:00"/>
+        <d v="2024-03-18T00:00:00"/>
+        <d v="2024-03-19T00:00:00"/>
+        <d v="2024-03-20T00:00:00"/>
+        <d v="2024-03-21T00:00:00"/>
+        <d v="2024-03-22T00:00:00"/>
+        <d v="2024-03-23T00:00:00"/>
+        <d v="2024-03-24T00:00:00"/>
+        <d v="2024-03-25T00:00:00"/>
+        <d v="2024-03-26T00:00:00"/>
+        <d v="2024-03-27T00:00:00"/>
+        <d v="2024-03-28T00:00:00"/>
+        <d v="2024-03-29T00:00:00"/>
+        <d v="2024-03-30T00:00:00"/>
+        <d v="2024-03-31T00:00:00"/>
+        <d v="2024-04-01T00:00:00"/>
+        <d v="2024-04-02T00:00:00"/>
+        <d v="2024-04-03T00:00:00"/>
+        <d v="2024-04-04T00:00:00"/>
+        <d v="2024-04-05T00:00:00"/>
+        <d v="2024-04-06T00:00:00"/>
+        <d v="2024-04-07T00:00:00"/>
+        <d v="2024-04-08T00:00:00"/>
+        <d v="2024-04-09T00:00:00"/>
+        <d v="2024-04-10T00:00:00"/>
+        <d v="2024-04-11T00:00:00"/>
+        <d v="2024-04-12T00:00:00"/>
+        <d v="2024-04-13T00:00:00"/>
+        <d v="2024-04-14T00:00:00"/>
+        <d v="2024-04-15T00:00:00"/>
+        <d v="2024-04-16T00:00:00"/>
+        <d v="2024-04-17T00:00:00"/>
+        <d v="2024-04-18T00:00:00"/>
+        <d v="2024-04-19T00:00:00"/>
+        <d v="2024-04-20T00:00:00"/>
+        <d v="2024-04-21T00:00:00"/>
+        <d v="2024-04-22T00:00:00"/>
+        <d v="2024-04-23T00:00:00"/>
+        <d v="2024-04-24T00:00:00"/>
+        <d v="2024-04-25T00:00:00"/>
+        <d v="2024-04-26T00:00:00"/>
+        <d v="2024-04-27T00:00:00"/>
+        <d v="2024-04-28T00:00:00"/>
+        <d v="2024-04-29T00:00:00"/>
+        <d v="2024-04-30T00:00:00"/>
+        <d v="2024-05-01T00:00:00"/>
+        <d v="2024-05-02T00:00:00"/>
+        <d v="2024-05-03T00:00:00"/>
+        <d v="2024-05-04T00:00:00"/>
+        <d v="2024-05-05T00:00:00"/>
+        <d v="2024-05-06T00:00:00"/>
+        <d v="2024-05-07T00:00:00"/>
+        <d v="2024-05-08T00:00:00"/>
+        <d v="2024-05-09T00:00:00"/>
+        <d v="2024-05-10T00:00:00"/>
+        <d v="2024-05-11T00:00:00"/>
+        <d v="2024-05-12T00:00:00"/>
+        <d v="2024-05-13T00:00:00"/>
+        <d v="2024-05-14T00:00:00"/>
+        <d v="2024-05-15T00:00:00"/>
+        <d v="2024-05-16T00:00:00"/>
+        <d v="2024-05-17T00:00:00"/>
+        <d v="2024-05-18T00:00:00"/>
+        <d v="2024-05-19T00:00:00"/>
+        <d v="2024-05-20T00:00:00"/>
+        <d v="2024-05-21T00:00:00"/>
+        <d v="2024-05-22T00:00:00"/>
+        <d v="2024-05-23T00:00:00"/>
+        <d v="2024-05-24T00:00:00"/>
+        <d v="2024-05-25T00:00:00"/>
+        <d v="2024-05-26T00:00:00"/>
+        <d v="2024-05-27T00:00:00"/>
+        <d v="2024-05-28T00:00:00"/>
+        <d v="2024-05-29T00:00:00"/>
+        <d v="2024-05-30T00:00:00"/>
+        <d v="2024-05-31T00:00:00"/>
+        <d v="2024-06-01T00:00:00"/>
+        <d v="2024-06-02T00:00:00"/>
+        <d v="2024-06-03T00:00:00"/>
+        <d v="2024-06-04T00:00:00"/>
+        <d v="2024-06-05T00:00:00"/>
+        <d v="2024-06-06T00:00:00"/>
+        <d v="2024-06-07T00:00:00"/>
+        <d v="2024-06-08T00:00:00"/>
+        <d v="2024-06-09T00:00:00"/>
+        <d v="2024-06-10T00:00:00"/>
+        <d v="2024-06-11T00:00:00"/>
+        <d v="2024-06-12T00:00:00"/>
+        <d v="2024-06-13T00:00:00"/>
+        <d v="2024-06-14T00:00:00"/>
+        <d v="2024-06-15T00:00:00"/>
+        <d v="2024-06-16T00:00:00"/>
+        <d v="2024-06-17T00:00:00"/>
+        <d v="2024-06-18T00:00:00"/>
+        <d v="2024-06-19T00:00:00"/>
+        <d v="2024-06-20T00:00:00"/>
+        <d v="2024-06-21T00:00:00"/>
+        <d v="2024-06-22T00:00:00"/>
+        <d v="2024-06-23T00:00:00"/>
+        <d v="2024-06-24T00:00:00"/>
+        <d v="2024-06-25T00:00:00"/>
+        <d v="2024-06-26T00:00:00"/>
+        <d v="2024-06-27T00:00:00"/>
+        <d v="2024-06-28T00:00:00"/>
+        <d v="2024-06-29T00:00:00"/>
+        <d v="2024-06-30T00:00:00"/>
+        <d v="2024-07-01T00:00:00"/>
+        <d v="2024-07-02T00:00:00"/>
+        <d v="2024-07-03T00:00:00"/>
+        <d v="2024-07-04T00:00:00"/>
+        <d v="2024-07-05T00:00:00"/>
+        <d v="2024-07-06T00:00:00"/>
+        <d v="2024-07-07T00:00:00"/>
+        <d v="2024-07-08T00:00:00"/>
+        <d v="2024-07-09T00:00:00"/>
+        <d v="2024-07-10T00:00:00"/>
+        <d v="2024-07-11T00:00:00"/>
+        <d v="2024-07-12T00:00:00"/>
+        <d v="2024-07-13T00:00:00"/>
+        <d v="2024-07-14T00:00:00"/>
+        <d v="2024-07-15T00:00:00"/>
+        <d v="2024-07-16T00:00:00"/>
+        <d v="2024-07-17T00:00:00"/>
+        <d v="2024-07-18T00:00:00"/>
+        <d v="2024-07-19T00:00:00"/>
+        <d v="2024-07-20T00:00:00"/>
+        <d v="2024-07-21T00:00:00"/>
+        <d v="2024-07-22T00:00:00"/>
+        <d v="2024-07-23T00:00:00"/>
+        <d v="2024-07-24T00:00:00"/>
+        <d v="2024-07-25T00:00:00"/>
+        <d v="2024-07-26T00:00:00"/>
+        <d v="2024-07-27T00:00:00"/>
+        <d v="2024-07-28T00:00:00"/>
+        <d v="2024-07-29T00:00:00"/>
+        <d v="2024-07-30T00:00:00"/>
+        <d v="2024-07-31T00:00:00"/>
+        <d v="2024-08-01T00:00:00"/>
+        <d v="2024-08-02T00:00:00"/>
+        <d v="2024-08-03T00:00:00"/>
+        <d v="2024-08-04T00:00:00"/>
+        <d v="2024-08-05T00:00:00"/>
+        <d v="2024-08-06T00:00:00"/>
+        <d v="2024-08-07T00:00:00"/>
+        <d v="2024-08-08T00:00:00"/>
+        <d v="2024-08-09T00:00:00"/>
+        <d v="2024-08-10T00:00:00"/>
+        <d v="2024-08-11T00:00:00"/>
+        <d v="2024-08-12T00:00:00"/>
+        <d v="2024-08-13T00:00:00"/>
+        <d v="2024-08-14T00:00:00"/>
+        <d v="2024-08-15T00:00:00"/>
+        <d v="2024-08-16T00:00:00"/>
+        <d v="2024-08-17T00:00:00"/>
+        <d v="2024-08-18T00:00:00"/>
+        <d v="2024-08-19T00:00:00"/>
+        <d v="2024-08-20T00:00:00"/>
+        <d v="2024-08-21T00:00:00"/>
+        <d v="2024-08-22T00:00:00"/>
+        <d v="2024-08-23T00:00:00"/>
+        <d v="2024-08-24T00:00:00"/>
+        <d v="2024-08-25T00:00:00"/>
+        <d v="2024-08-26T00:00:00"/>
+        <d v="2024-08-27T00:00:00"/>
+        <d v="2024-08-28T00:00:00"/>
+        <d v="2024-08-29T00:00:00"/>
+        <d v="2024-08-30T00:00:00"/>
+        <d v="2024-08-31T00:00:00"/>
+        <d v="2024-09-01T00:00:00"/>
+        <d v="2024-09-02T00:00:00"/>
+        <d v="2024-09-03T00:00:00"/>
+        <d v="2024-09-04T00:00:00"/>
+        <d v="2024-09-05T00:00:00"/>
+        <d v="2024-09-06T00:00:00"/>
+        <d v="2024-09-07T00:00:00"/>
+        <d v="2024-09-08T00:00:00"/>
+        <d v="2024-09-09T00:00:00"/>
+        <d v="2024-09-10T00:00:00"/>
+        <d v="2024-09-11T00:00:00"/>
+        <d v="2024-09-12T00:00:00"/>
+        <d v="2024-09-13T00:00:00"/>
+        <d v="2024-09-14T00:00:00"/>
+        <d v="2024-09-15T00:00:00"/>
+        <d v="2024-09-16T00:00:00"/>
+        <d v="2024-09-17T00:00:00"/>
+        <d v="2024-09-18T00:00:00"/>
+        <d v="2024-09-19T00:00:00"/>
+        <d v="2024-09-20T00:00:00"/>
+        <d v="2024-09-21T00:00:00"/>
+        <d v="2024-09-22T00:00:00"/>
+        <d v="2024-09-23T00:00:00"/>
+        <d v="2024-09-24T00:00:00"/>
+        <d v="2024-09-25T00:00:00"/>
+        <d v="2024-09-26T00:00:00"/>
+        <d v="2024-09-27T00:00:00"/>
+        <d v="2024-09-28T00:00:00"/>
+        <d v="2024-09-29T00:00:00"/>
+        <d v="2024-09-30T00:00:00"/>
+        <d v="2024-10-01T00:00:00"/>
+        <d v="2024-10-02T00:00:00"/>
+        <d v="2024-10-03T00:00:00"/>
+        <d v="2024-10-04T00:00:00"/>
+        <d v="2024-10-05T00:00:00"/>
+        <d v="2024-10-06T00:00:00"/>
+        <d v="2024-10-07T00:00:00"/>
+        <d v="2024-10-08T00:00:00"/>
+        <d v="2024-10-09T00:00:00"/>
+        <d v="2024-10-10T00:00:00"/>
+        <d v="2024-10-11T00:00:00"/>
+        <d v="2024-10-12T00:00:00"/>
+        <d v="2024-10-13T00:00:00"/>
+        <d v="2024-10-14T00:00:00"/>
+        <d v="2024-10-15T00:00:00"/>
+        <d v="2024-10-16T00:00:00"/>
+        <d v="2024-10-17T00:00:00"/>
+        <d v="2024-10-18T00:00:00"/>
+        <d v="2024-10-19T00:00:00"/>
+        <d v="2024-10-20T00:00:00"/>
+        <d v="2024-10-21T00:00:00"/>
+        <d v="2024-10-22T00:00:00"/>
+        <d v="2024-10-23T00:00:00"/>
+        <d v="2024-10-24T00:00:00"/>
+        <d v="2024-10-25T00:00:00"/>
+        <d v="2024-10-26T00:00:00"/>
+        <d v="2024-10-27T00:00:00"/>
+        <d v="2024-10-28T00:00:00"/>
+        <d v="2024-10-29T00:00:00"/>
+        <d v="2024-10-30T00:00:00"/>
+        <d v="2024-10-31T00:00:00"/>
+        <d v="2024-11-01T00:00:00"/>
+        <d v="2024-11-02T00:00:00"/>
+        <d v="2024-11-03T00:00:00"/>
+        <d v="2024-11-04T00:00:00"/>
+        <d v="2024-11-05T00:00:00"/>
+        <d v="2024-11-06T00:00:00"/>
+        <d v="2024-11-07T00:00:00"/>
+        <d v="2024-11-08T00:00:00"/>
+        <d v="2024-11-09T00:00:00"/>
+        <d v="2024-11-10T00:00:00"/>
+        <d v="2024-11-11T00:00:00"/>
+        <d v="2024-11-12T00:00:00"/>
+        <d v="2024-11-13T00:00:00"/>
+        <d v="2024-11-14T00:00:00"/>
+        <d v="2024-11-15T00:00:00"/>
+        <d v="2024-11-16T00:00:00"/>
+        <d v="2024-11-17T00:00:00"/>
+        <d v="2024-11-18T00:00:00"/>
+        <d v="2024-11-19T00:00:00"/>
+        <d v="2024-11-20T00:00:00"/>
+        <d v="2024-11-21T00:00:00"/>
+        <d v="2024-11-22T00:00:00"/>
+        <d v="2024-11-23T00:00:00"/>
+        <d v="2024-11-24T00:00:00"/>
+        <d v="2024-11-25T00:00:00"/>
+        <d v="2024-11-26T00:00:00"/>
+        <d v="2024-11-27T00:00:00"/>
+        <d v="2024-11-28T00:00:00"/>
+        <d v="2024-11-29T00:00:00"/>
+        <d v="2024-11-30T00:00:00"/>
+        <d v="2024-12-01T00:00:00"/>
+        <d v="2024-12-02T00:00:00"/>
+        <d v="2024-12-03T00:00:00"/>
+        <d v="2024-12-04T00:00:00"/>
+        <d v="2024-12-05T00:00:00"/>
+        <d v="2024-12-06T00:00:00"/>
+        <d v="2024-12-07T00:00:00"/>
+        <d v="2024-12-08T00:00:00"/>
+        <d v="2024-12-09T00:00:00"/>
+        <d v="2024-12-10T00:00:00"/>
+        <d v="2024-12-11T00:00:00"/>
+        <d v="2024-12-12T00:00:00"/>
+        <d v="2024-12-13T00:00:00"/>
+        <d v="2024-12-14T00:00:00"/>
+        <d v="2024-12-15T00:00:00"/>
+        <d v="2024-12-16T00:00:00"/>
+      </sharedItems>
     </cacheField>
     <cacheField name="Auto Renewal" numFmtId="0">
       <sharedItems count="2">
@@ -5708,7 +6676,11 @@
       <sharedItems containsSemiMixedTypes="0" containsString="0" containsNumber="1" containsInteger="1" minValue="5" maxValue="15"/>
     </cacheField>
     <cacheField name="Subscription Type" numFmtId="0">
-      <sharedItems/>
+      <sharedItems count="3">
+        <s v="Monthly"/>
+        <s v="Annual"/>
+        <s v="Quarterly"/>
+      </sharedItems>
     </cacheField>
     <cacheField name="EA Play Season Pass" numFmtId="0">
       <sharedItems/>
@@ -5731,7 +6703,7 @@
   </cacheFields>
   <extLst>
     <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{725AE2AE-9491-48be-B2B4-4EB974FC3084}">
-      <x14:pivotCacheDefinition/>
+      <x14:pivotCacheDefinition pivotCacheId="1683066976"/>
     </ext>
   </extLst>
 </pivotCacheDefinition>
@@ -5743,7 +6715,7 @@
     <n v="3231"/>
     <s v="João Silva"/>
     <x v="0"/>
-    <d v="2024-01-01T00:00:00"/>
+    <x v="0"/>
     <x v="0"/>
     <n v="15"/>
     <s v="Monthly"/>
@@ -5758,7 +6730,7 @@
     <n v="3232"/>
     <s v="Maria Oliveira"/>
     <x v="1"/>
-    <d v="2024-01-15T00:00:00"/>
+    <x v="1"/>
     <x v="1"/>
     <n v="5"/>
     <s v="Annual"/>
@@ -5773,7 +6745,7 @@
     <n v="3233"/>
     <s v="Lucas Fernandes"/>
     <x v="2"/>
-    <d v="2024-02-10T00:00:00"/>
+    <x v="2"/>
     <x v="0"/>
     <n v="10"/>
     <s v="Quarterly"/>
@@ -5788,7 +6760,7 @@
     <n v="3234"/>
     <s v="Ana Souza"/>
     <x v="0"/>
-    <d v="2024-02-20T00:00:00"/>
+    <x v="3"/>
     <x v="1"/>
     <n v="15"/>
     <s v="Monthly"/>
@@ -5803,7 +6775,7 @@
     <n v="3235"/>
     <s v="Pedro Gonçalves"/>
     <x v="1"/>
-    <d v="2024-03-05T00:00:00"/>
+    <x v="4"/>
     <x v="0"/>
     <n v="5"/>
     <s v="Monthly"/>
@@ -5818,7 +6790,7 @@
     <n v="3236"/>
     <s v="Felipe Costa"/>
     <x v="2"/>
-    <d v="2024-03-02T00:00:00"/>
+    <x v="5"/>
     <x v="1"/>
     <n v="10"/>
     <s v="Monthly"/>
@@ -5833,7 +6805,7 @@
     <n v="3237"/>
     <s v="Camila Ribeiro"/>
     <x v="0"/>
-    <d v="2024-03-03T00:00:00"/>
+    <x v="6"/>
     <x v="0"/>
     <n v="15"/>
     <s v="Quarterly"/>
@@ -5848,7 +6820,7 @@
     <n v="3238"/>
     <s v="André Mendes"/>
     <x v="1"/>
-    <d v="2024-03-04T00:00:00"/>
+    <x v="7"/>
     <x v="0"/>
     <n v="5"/>
     <s v="Annual"/>
@@ -5863,7 +6835,7 @@
     <n v="3239"/>
     <s v="Sofia Almeida"/>
     <x v="0"/>
-    <d v="2024-03-05T00:00:00"/>
+    <x v="4"/>
     <x v="1"/>
     <n v="15"/>
     <s v="Monthly"/>
@@ -5878,7 +6850,7 @@
     <n v="3240"/>
     <s v="Bruno Martins"/>
     <x v="2"/>
-    <d v="2024-03-06T00:00:00"/>
+    <x v="8"/>
     <x v="0"/>
     <n v="10"/>
     <s v="Quarterly"/>
@@ -5893,7 +6865,7 @@
     <n v="3241"/>
     <s v="Rita Castro"/>
     <x v="1"/>
-    <d v="2024-03-07T00:00:00"/>
+    <x v="9"/>
     <x v="1"/>
     <n v="5"/>
     <s v="Monthly"/>
@@ -5908,7 +6880,7 @@
     <n v="3242"/>
     <s v="Marco Túlio"/>
     <x v="0"/>
-    <d v="2024-03-08T00:00:00"/>
+    <x v="10"/>
     <x v="0"/>
     <n v="15"/>
     <s v="Annual"/>
@@ -5923,7 +6895,7 @@
     <n v="3243"/>
     <s v="Lívia Silveira"/>
     <x v="2"/>
-    <d v="2024-03-09T00:00:00"/>
+    <x v="11"/>
     <x v="1"/>
     <n v="10"/>
     <s v="Monthly"/>
@@ -5938,7 +6910,7 @@
     <n v="3244"/>
     <s v="Diogo Sousa"/>
     <x v="1"/>
-    <d v="2024-03-10T00:00:00"/>
+    <x v="12"/>
     <x v="0"/>
     <n v="5"/>
     <s v="Quarterly"/>
@@ -5953,7 +6925,7 @@
     <n v="3245"/>
     <s v="Fernanda Lima"/>
     <x v="0"/>
-    <d v="2024-03-11T00:00:00"/>
+    <x v="13"/>
     <x v="1"/>
     <n v="15"/>
     <s v="Monthly"/>
@@ -5968,7 +6940,7 @@
     <n v="3246"/>
     <s v="Caio Pereira"/>
     <x v="2"/>
-    <d v="2024-03-12T00:00:00"/>
+    <x v="14"/>
     <x v="0"/>
     <n v="10"/>
     <s v="Annual"/>
@@ -5983,7 +6955,7 @@
     <n v="3247"/>
     <s v="Beatriz Gomes"/>
     <x v="1"/>
-    <d v="2024-03-13T00:00:00"/>
+    <x v="15"/>
     <x v="1"/>
     <n v="5"/>
     <s v="Monthly"/>
@@ -5998,7 +6970,7 @@
     <n v="3248"/>
     <s v="Cesar Oliveira"/>
     <x v="0"/>
-    <d v="2024-03-14T00:00:00"/>
+    <x v="16"/>
     <x v="0"/>
     <n v="15"/>
     <s v="Quarterly"/>
@@ -6013,7 +6985,7 @@
     <n v="3249"/>
     <s v="Débora Machado"/>
     <x v="2"/>
-    <d v="2024-03-15T00:00:00"/>
+    <x v="17"/>
     <x v="1"/>
     <n v="10"/>
     <s v="Monthly"/>
@@ -6028,7 +7000,7 @@
     <n v="3250"/>
     <s v="Eduardo Vargas"/>
     <x v="1"/>
-    <d v="2024-03-16T00:00:00"/>
+    <x v="18"/>
     <x v="0"/>
     <n v="5"/>
     <s v="Annual"/>
@@ -6043,7 +7015,7 @@
     <n v="3251"/>
     <s v="Gabriela Santos"/>
     <x v="0"/>
-    <d v="2024-03-17T00:00:00"/>
+    <x v="19"/>
     <x v="1"/>
     <n v="15"/>
     <s v="Monthly"/>
@@ -6058,7 +7030,7 @@
     <n v="3252"/>
     <s v="Henrique Dias"/>
     <x v="2"/>
-    <d v="2024-03-18T00:00:00"/>
+    <x v="20"/>
     <x v="0"/>
     <n v="10"/>
     <s v="Quarterly"/>
@@ -6073,7 +7045,7 @@
     <n v="3253"/>
     <s v="Isabela Moreira"/>
     <x v="1"/>
-    <d v="2024-03-19T00:00:00"/>
+    <x v="21"/>
     <x v="1"/>
     <n v="5"/>
     <s v="Monthly"/>
@@ -6088,7 +7060,7 @@
     <n v="3254"/>
     <s v="Joaquim Barbosa"/>
     <x v="0"/>
-    <d v="2024-03-20T00:00:00"/>
+    <x v="22"/>
     <x v="0"/>
     <n v="15"/>
     <s v="Annual"/>
@@ -6103,7 +7075,7 @@
     <n v="3255"/>
     <s v="Lara Rocha"/>
     <x v="2"/>
-    <d v="2024-03-21T00:00:00"/>
+    <x v="23"/>
     <x v="1"/>
     <n v="10"/>
     <s v="Monthly"/>
@@ -6118,7 +7090,7 @@
     <n v="3256"/>
     <s v="Matheus Silva"/>
     <x v="1"/>
-    <d v="2024-03-22T00:00:00"/>
+    <x v="24"/>
     <x v="0"/>
     <n v="5"/>
     <s v="Quarterly"/>
@@ -6133,7 +7105,7 @@
     <n v="3257"/>
     <s v="Nicole Costa"/>
     <x v="0"/>
-    <d v="2024-03-23T00:00:00"/>
+    <x v="25"/>
     <x v="1"/>
     <n v="15"/>
     <s v="Monthly"/>
@@ -6148,7 +7120,7 @@
     <n v="3258"/>
     <s v="Otávio Mendonça"/>
     <x v="2"/>
-    <d v="2024-03-24T00:00:00"/>
+    <x v="26"/>
     <x v="0"/>
     <n v="10"/>
     <s v="Annual"/>
@@ -6163,7 +7135,7 @@
     <n v="3259"/>
     <s v="Paula Ferreira"/>
     <x v="1"/>
-    <d v="2024-03-25T00:00:00"/>
+    <x v="27"/>
     <x v="1"/>
     <n v="5"/>
     <s v="Monthly"/>
@@ -6178,7 +7150,7 @@
     <n v="3260"/>
     <s v="Raquel Alves"/>
     <x v="0"/>
-    <d v="2024-03-26T00:00:00"/>
+    <x v="28"/>
     <x v="0"/>
     <n v="15"/>
     <s v="Quarterly"/>
@@ -6193,7 +7165,7 @@
     <n v="3261"/>
     <s v="Samuel Pires"/>
     <x v="2"/>
-    <d v="2024-03-27T00:00:00"/>
+    <x v="29"/>
     <x v="1"/>
     <n v="10"/>
     <s v="Monthly"/>
@@ -6208,7 +7180,7 @@
     <n v="3262"/>
     <s v="Tânia Barros"/>
     <x v="1"/>
-    <d v="2024-03-28T00:00:00"/>
+    <x v="30"/>
     <x v="0"/>
     <n v="5"/>
     <s v="Annual"/>
@@ -6223,7 +7195,7 @@
     <n v="3263"/>
     <s v="Vinicius Lima"/>
     <x v="0"/>
-    <d v="2024-03-29T00:00:00"/>
+    <x v="31"/>
     <x v="1"/>
     <n v="15"/>
     <s v="Monthly"/>
@@ -6238,7 +7210,7 @@
     <n v="3264"/>
     <s v="Yasmin Teixeira"/>
     <x v="2"/>
-    <d v="2024-03-30T00:00:00"/>
+    <x v="32"/>
     <x v="0"/>
     <n v="10"/>
     <s v="Quarterly"/>
@@ -6253,7 +7225,7 @@
     <n v="3265"/>
     <s v="Zé Carlos"/>
     <x v="1"/>
-    <d v="2024-03-31T00:00:00"/>
+    <x v="33"/>
     <x v="1"/>
     <n v="5"/>
     <s v="Monthly"/>
@@ -6268,7 +7240,7 @@
     <n v="3266"/>
     <s v="Amanda Nogueira"/>
     <x v="1"/>
-    <d v="2024-04-01T00:00:00"/>
+    <x v="34"/>
     <x v="0"/>
     <n v="5"/>
     <s v="Monthly"/>
@@ -6283,7 +7255,7 @@
     <n v="3267"/>
     <s v="Bruno Cavalheiro"/>
     <x v="0"/>
-    <d v="2024-04-02T00:00:00"/>
+    <x v="35"/>
     <x v="1"/>
     <n v="15"/>
     <s v="Quarterly"/>
@@ -6298,7 +7270,7 @@
     <n v="3268"/>
     <s v="Carla Dias"/>
     <x v="2"/>
-    <d v="2024-04-03T00:00:00"/>
+    <x v="36"/>
     <x v="0"/>
     <n v="10"/>
     <s v="Annual"/>
@@ -6313,7 +7285,7 @@
     <n v="3269"/>
     <s v="Diego Fontes"/>
     <x v="1"/>
-    <d v="2024-04-04T00:00:00"/>
+    <x v="37"/>
     <x v="1"/>
     <n v="5"/>
     <s v="Quarterly"/>
@@ -6328,7 +7300,7 @@
     <n v="3270"/>
     <s v="Eunice Lima"/>
     <x v="0"/>
-    <d v="2024-04-05T00:00:00"/>
+    <x v="38"/>
     <x v="0"/>
     <n v="15"/>
     <s v="Monthly"/>
@@ -6343,7 +7315,7 @@
     <n v="3271"/>
     <s v="Fábio Martins"/>
     <x v="2"/>
-    <d v="2024-04-06T00:00:00"/>
+    <x v="39"/>
     <x v="1"/>
     <n v="10"/>
     <s v="Monthly"/>
@@ -6358,7 +7330,7 @@
     <n v="3272"/>
     <s v="Gisele Araújo"/>
     <x v="1"/>
-    <d v="2024-04-07T00:00:00"/>
+    <x v="40"/>
     <x v="0"/>
     <n v="5"/>
     <s v="Annual"/>
@@ -6373,7 +7345,7 @@
     <n v="3273"/>
     <s v="Hélio Castro"/>
     <x v="0"/>
-    <d v="2024-04-08T00:00:00"/>
+    <x v="41"/>
     <x v="1"/>
     <n v="15"/>
     <s v="Quarterly"/>
@@ -6388,7 +7360,7 @@
     <n v="3274"/>
     <s v="Ingrid Menezes"/>
     <x v="2"/>
-    <d v="2024-04-09T00:00:00"/>
+    <x v="42"/>
     <x v="0"/>
     <n v="10"/>
     <s v="Quarterly"/>
@@ -6403,7 +7375,7 @@
     <n v="3275"/>
     <s v="Jorge Baptista"/>
     <x v="1"/>
-    <d v="2024-04-10T00:00:00"/>
+    <x v="43"/>
     <x v="1"/>
     <n v="5"/>
     <s v="Monthly"/>
@@ -6418,7 +7390,7 @@
     <n v="3276"/>
     <s v="Kléber Oliveira"/>
     <x v="0"/>
-    <d v="2024-04-11T00:00:00"/>
+    <x v="44"/>
     <x v="0"/>
     <n v="15"/>
     <s v="Annual"/>
@@ -6433,7 +7405,7 @@
     <n v="3277"/>
     <s v="Luciana Freitas"/>
     <x v="2"/>
-    <d v="2024-04-12T00:00:00"/>
+    <x v="45"/>
     <x v="1"/>
     <n v="10"/>
     <s v="Monthly"/>
@@ -6448,7 +7420,7 @@
     <n v="3278"/>
     <s v="Márcia Eller"/>
     <x v="1"/>
-    <d v="2024-04-13T00:00:00"/>
+    <x v="46"/>
     <x v="0"/>
     <n v="5"/>
     <s v="Quarterly"/>
@@ -6463,7 +7435,7 @@
     <n v="3279"/>
     <s v="Nilo Peçanha"/>
     <x v="0"/>
-    <d v="2024-04-14T00:00:00"/>
+    <x v="47"/>
     <x v="1"/>
     <n v="15"/>
     <s v="Monthly"/>
@@ -6478,7 +7450,7 @@
     <n v="3280"/>
     <s v="Oscar Neves"/>
     <x v="2"/>
-    <d v="2024-04-15T00:00:00"/>
+    <x v="48"/>
     <x v="0"/>
     <n v="10"/>
     <s v="Annual"/>
@@ -6493,7 +7465,7 @@
     <n v="3281"/>
     <s v="Patrícia Soares"/>
     <x v="1"/>
-    <d v="2024-04-16T00:00:00"/>
+    <x v="49"/>
     <x v="1"/>
     <n v="5"/>
     <s v="Monthly"/>
@@ -6508,7 +7480,7 @@
     <n v="3282"/>
     <s v="Quirino Gonçalves"/>
     <x v="0"/>
-    <d v="2024-04-17T00:00:00"/>
+    <x v="50"/>
     <x v="0"/>
     <n v="15"/>
     <s v="Quarterly"/>
@@ -6523,7 +7495,7 @@
     <n v="3283"/>
     <s v="Raul Machado"/>
     <x v="2"/>
-    <d v="2024-04-18T00:00:00"/>
+    <x v="51"/>
     <x v="1"/>
     <n v="10"/>
     <s v="Monthly"/>
@@ -6538,7 +7510,7 @@
     <n v="3284"/>
     <s v="Sônia Lobo"/>
     <x v="1"/>
-    <d v="2024-04-19T00:00:00"/>
+    <x v="52"/>
     <x v="0"/>
     <n v="5"/>
     <s v="Annual"/>
@@ -6553,7 +7525,7 @@
     <n v="3285"/>
     <s v="Tiago Ramos"/>
     <x v="0"/>
-    <d v="2024-04-20T00:00:00"/>
+    <x v="53"/>
     <x v="1"/>
     <n v="15"/>
     <s v="Monthly"/>
@@ -6568,7 +7540,7 @@
     <n v="3286"/>
     <s v="Ugo Pires"/>
     <x v="2"/>
-    <d v="2024-04-21T00:00:00"/>
+    <x v="54"/>
     <x v="0"/>
     <n v="10"/>
     <s v="Quarterly"/>
@@ -6583,7 +7555,7 @@
     <n v="3287"/>
     <s v="Valéria Nobre"/>
     <x v="1"/>
-    <d v="2024-04-22T00:00:00"/>
+    <x v="55"/>
     <x v="1"/>
     <n v="5"/>
     <s v="Monthly"/>
@@ -6598,7 +7570,7 @@
     <n v="3288"/>
     <s v="William Siqueira"/>
     <x v="0"/>
-    <d v="2024-04-23T00:00:00"/>
+    <x v="56"/>
     <x v="0"/>
     <n v="15"/>
     <s v="Annual"/>
@@ -6613,7 +7585,7 @@
     <n v="3289"/>
     <s v="Xuxa Meneghel"/>
     <x v="2"/>
-    <d v="2024-04-24T00:00:00"/>
+    <x v="57"/>
     <x v="1"/>
     <n v="10"/>
     <s v="Monthly"/>
@@ -6628,7 +7600,7 @@
     <n v="3290"/>
     <s v="Yara Figueiredo"/>
     <x v="1"/>
-    <d v="2024-04-25T00:00:00"/>
+    <x v="58"/>
     <x v="0"/>
     <n v="5"/>
     <s v="Quarterly"/>
@@ -6643,7 +7615,7 @@
     <n v="3291"/>
     <s v="Zacarias Alves"/>
     <x v="0"/>
-    <d v="2024-04-26T00:00:00"/>
+    <x v="59"/>
     <x v="1"/>
     <n v="15"/>
     <s v="Monthly"/>
@@ -6658,7 +7630,7 @@
     <n v="3292"/>
     <s v="Amanda Bynes"/>
     <x v="2"/>
-    <d v="2024-04-27T00:00:00"/>
+    <x v="60"/>
     <x v="0"/>
     <n v="10"/>
     <s v="Annual"/>
@@ -6673,7 +7645,7 @@
     <n v="3293"/>
     <s v="Bruno Mars"/>
     <x v="1"/>
-    <d v="2024-04-28T00:00:00"/>
+    <x v="61"/>
     <x v="1"/>
     <n v="5"/>
     <s v="Monthly"/>
@@ -6688,7 +7660,7 @@
     <n v="3294"/>
     <s v="Carla Bruni"/>
     <x v="0"/>
-    <d v="2024-04-29T00:00:00"/>
+    <x v="62"/>
     <x v="0"/>
     <n v="15"/>
     <s v="Quarterly"/>
@@ -6703,7 +7675,7 @@
     <n v="3295"/>
     <s v="Diego Maradona"/>
     <x v="2"/>
-    <d v="2024-04-30T00:00:00"/>
+    <x v="63"/>
     <x v="1"/>
     <n v="10"/>
     <s v="Monthly"/>
@@ -6718,7 +7690,7 @@
     <n v="3296"/>
     <s v="Estela Marques"/>
     <x v="1"/>
-    <d v="2024-05-01T00:00:00"/>
+    <x v="64"/>
     <x v="1"/>
     <n v="5"/>
     <s v="Monthly"/>
@@ -6733,7 +7705,7 @@
     <n v="3297"/>
     <s v="Fábio Nobre"/>
     <x v="0"/>
-    <d v="2024-05-02T00:00:00"/>
+    <x v="65"/>
     <x v="0"/>
     <n v="15"/>
     <s v="Quarterly"/>
@@ -6748,7 +7720,7 @@
     <n v="3298"/>
     <s v="Gabriel Oliveira"/>
     <x v="2"/>
-    <d v="2024-05-03T00:00:00"/>
+    <x v="66"/>
     <x v="1"/>
     <n v="10"/>
     <s v="Annual"/>
@@ -6763,7 +7735,7 @@
     <n v="3299"/>
     <s v="Helena Santos"/>
     <x v="1"/>
-    <d v="2024-05-04T00:00:00"/>
+    <x v="67"/>
     <x v="0"/>
     <n v="5"/>
     <s v="Quarterly"/>
@@ -6778,7 +7750,7 @@
     <n v="3300"/>
     <s v="Ivan Carvalho"/>
     <x v="0"/>
-    <d v="2024-05-05T00:00:00"/>
+    <x v="68"/>
     <x v="1"/>
     <n v="15"/>
     <s v="Monthly"/>
@@ -6793,7 +7765,7 @@
     <n v="3301"/>
     <s v="Júlia Ferreira"/>
     <x v="2"/>
-    <d v="2024-05-06T00:00:00"/>
+    <x v="69"/>
     <x v="0"/>
     <n v="10"/>
     <s v="Monthly"/>
@@ -6808,7 +7780,7 @@
     <n v="3302"/>
     <s v="Karla Alves"/>
     <x v="1"/>
-    <d v="2024-05-07T00:00:00"/>
+    <x v="70"/>
     <x v="1"/>
     <n v="5"/>
     <s v="Annual"/>
@@ -6823,7 +7795,7 @@
     <n v="3303"/>
     <s v="Lucas Mendes"/>
     <x v="0"/>
-    <d v="2024-05-08T00:00:00"/>
+    <x v="71"/>
     <x v="0"/>
     <n v="15"/>
     <s v="Quarterly"/>
@@ -6838,7 +7810,7 @@
     <n v="3304"/>
     <s v="Mônica Gomes"/>
     <x v="2"/>
-    <d v="2024-05-09T00:00:00"/>
+    <x v="72"/>
     <x v="1"/>
     <n v="10"/>
     <s v="Quarterly"/>
@@ -6853,7 +7825,7 @@
     <n v="3305"/>
     <s v="Norberto Queiroz"/>
     <x v="1"/>
-    <d v="2024-05-10T00:00:00"/>
+    <x v="73"/>
     <x v="0"/>
     <n v="5"/>
     <s v="Monthly"/>
@@ -6868,7 +7840,7 @@
     <n v="3306"/>
     <s v="Otávio Barros"/>
     <x v="0"/>
-    <d v="2024-05-11T00:00:00"/>
+    <x v="74"/>
     <x v="1"/>
     <n v="15"/>
     <s v="Annual"/>
@@ -6883,7 +7855,7 @@
     <n v="3307"/>
     <s v="Paula Vieira"/>
     <x v="2"/>
-    <d v="2024-05-12T00:00:00"/>
+    <x v="75"/>
     <x v="0"/>
     <n v="10"/>
     <s v="Monthly"/>
@@ -6898,7 +7870,7 @@
     <n v="3308"/>
     <s v="Quentin Ramos"/>
     <x v="1"/>
-    <d v="2024-05-13T00:00:00"/>
+    <x v="76"/>
     <x v="1"/>
     <n v="5"/>
     <s v="Quarterly"/>
@@ -6913,7 +7885,7 @@
     <n v="3309"/>
     <s v="Raquel Novaes"/>
     <x v="0"/>
-    <d v="2024-05-14T00:00:00"/>
+    <x v="77"/>
     <x v="0"/>
     <n v="15"/>
     <s v="Monthly"/>
@@ -6928,7 +7900,7 @@
     <n v="3310"/>
     <s v="Samantha Lopes"/>
     <x v="2"/>
-    <d v="2024-05-15T00:00:00"/>
+    <x v="78"/>
     <x v="1"/>
     <n v="10"/>
     <s v="Annual"/>
@@ -6943,7 +7915,7 @@
     <n v="3311"/>
     <s v="Tiago Martins"/>
     <x v="1"/>
-    <d v="2024-05-16T00:00:00"/>
+    <x v="79"/>
     <x v="0"/>
     <n v="5"/>
     <s v="Monthly"/>
@@ -6958,7 +7930,7 @@
     <n v="3312"/>
     <s v="Ulysses Guimarães"/>
     <x v="0"/>
-    <d v="2024-05-17T00:00:00"/>
+    <x v="80"/>
     <x v="1"/>
     <n v="15"/>
     <s v="Quarterly"/>
@@ -6973,7 +7945,7 @@
     <n v="3313"/>
     <s v="Vanessa Silva"/>
     <x v="2"/>
-    <d v="2024-05-18T00:00:00"/>
+    <x v="81"/>
     <x v="0"/>
     <n v="10"/>
     <s v="Monthly"/>
@@ -6988,7 +7960,7 @@
     <n v="3314"/>
     <s v="William Carneiro"/>
     <x v="1"/>
-    <d v="2024-05-19T00:00:00"/>
+    <x v="82"/>
     <x v="1"/>
     <n v="5"/>
     <s v="Annual"/>
@@ -7003,7 +7975,7 @@
     <n v="3315"/>
     <s v="Ximena Rocha"/>
     <x v="0"/>
-    <d v="2024-05-20T00:00:00"/>
+    <x v="83"/>
     <x v="0"/>
     <n v="15"/>
     <s v="Monthly"/>
@@ -7018,7 +7990,7 @@
     <n v="3316"/>
     <s v="Yasmin Figueiredo"/>
     <x v="2"/>
-    <d v="2024-05-21T00:00:00"/>
+    <x v="84"/>
     <x v="1"/>
     <n v="10"/>
     <s v="Quarterly"/>
@@ -7033,7 +8005,7 @@
     <n v="3317"/>
     <s v="Zara Cunha"/>
     <x v="1"/>
-    <d v="2024-05-22T00:00:00"/>
+    <x v="85"/>
     <x v="0"/>
     <n v="5"/>
     <s v="Monthly"/>
@@ -7048,7 +8020,7 @@
     <n v="3318"/>
     <s v="Alan Teixeira"/>
     <x v="0"/>
-    <d v="2024-05-23T00:00:00"/>
+    <x v="86"/>
     <x v="1"/>
     <n v="15"/>
     <s v="Annual"/>
@@ -7063,7 +8035,7 @@
     <n v="3319"/>
     <s v="Bárbara Oliveira"/>
     <x v="2"/>
-    <d v="2024-05-24T00:00:00"/>
+    <x v="87"/>
     <x v="0"/>
     <n v="10"/>
     <s v="Monthly"/>
@@ -7078,7 +8050,7 @@
     <n v="3320"/>
     <s v="Carlos Junqueira"/>
     <x v="1"/>
-    <d v="2024-05-25T00:00:00"/>
+    <x v="88"/>
     <x v="1"/>
     <n v="5"/>
     <s v="Quarterly"/>
@@ -7093,7 +8065,7 @@
     <n v="3321"/>
     <s v="Daniela Moura"/>
     <x v="0"/>
-    <d v="2024-05-26T00:00:00"/>
+    <x v="89"/>
     <x v="0"/>
     <n v="15"/>
     <s v="Monthly"/>
@@ -7108,7 +8080,7 @@
     <n v="3322"/>
     <s v="Eduardo Lima"/>
     <x v="2"/>
-    <d v="2024-05-27T00:00:00"/>
+    <x v="90"/>
     <x v="1"/>
     <n v="10"/>
     <s v="Annual"/>
@@ -7123,7 +8095,7 @@
     <n v="3323"/>
     <s v="Fabiana Araújo"/>
     <x v="1"/>
-    <d v="2024-05-28T00:00:00"/>
+    <x v="91"/>
     <x v="0"/>
     <n v="5"/>
     <s v="Monthly"/>
@@ -7138,7 +8110,7 @@
     <n v="3324"/>
     <s v="Geraldo Ribeiro"/>
     <x v="0"/>
-    <d v="2024-05-29T00:00:00"/>
+    <x v="92"/>
     <x v="1"/>
     <n v="15"/>
     <s v="Quarterly"/>
@@ -7153,7 +8125,7 @@
     <n v="3325"/>
     <s v="Héctor Vargas"/>
     <x v="2"/>
-    <d v="2024-05-30T00:00:00"/>
+    <x v="93"/>
     <x v="0"/>
     <n v="10"/>
     <s v="Quarterly"/>
@@ -7168,7 +8140,7 @@
     <n v="3326"/>
     <s v="Isabela Fonseca"/>
     <x v="1"/>
-    <d v="2024-05-31T00:00:00"/>
+    <x v="94"/>
     <x v="1"/>
     <n v="5"/>
     <s v="Annual"/>
@@ -7183,7 +8155,7 @@
     <n v="3327"/>
     <s v="João Pedro Almeida"/>
     <x v="0"/>
-    <d v="2024-06-01T00:00:00"/>
+    <x v="95"/>
     <x v="0"/>
     <n v="15"/>
     <s v="Monthly"/>
@@ -7198,7 +8170,7 @@
     <n v="3328"/>
     <s v="Klara Costa"/>
     <x v="2"/>
-    <d v="2024-06-02T00:00:00"/>
+    <x v="96"/>
     <x v="1"/>
     <n v="10"/>
     <s v="Annual"/>
@@ -7213,7 +8185,7 @@
     <n v="3329"/>
     <s v="Luciana Mendes"/>
     <x v="1"/>
-    <d v="2024-06-03T00:00:00"/>
+    <x v="97"/>
     <x v="0"/>
     <n v="5"/>
     <s v="Quarterly"/>
@@ -7228,7 +8200,7 @@
     <n v="3330"/>
     <s v="Marcelo Gouveia"/>
     <x v="0"/>
-    <d v="2024-06-04T00:00:00"/>
+    <x v="98"/>
     <x v="1"/>
     <n v="15"/>
     <s v="Monthly"/>
@@ -7243,7 +8215,7 @@
     <n v="3331"/>
     <s v="Nívea Borges"/>
     <x v="2"/>
-    <d v="2024-06-05T00:00:00"/>
+    <x v="99"/>
     <x v="0"/>
     <n v="10"/>
     <s v="Monthly"/>
@@ -7258,7 +8230,7 @@
     <n v="3332"/>
     <s v="Oscar Nogueira"/>
     <x v="1"/>
-    <d v="2024-06-06T00:00:00"/>
+    <x v="100"/>
     <x v="1"/>
     <n v="5"/>
     <s v="Annual"/>
@@ -7273,7 +8245,7 @@
     <n v="3333"/>
     <s v="Patrícia Alves"/>
     <x v="0"/>
-    <d v="2024-06-07T00:00:00"/>
+    <x v="101"/>
     <x v="0"/>
     <n v="15"/>
     <s v="Quarterly"/>
@@ -7288,7 +8260,7 @@
     <n v="3334"/>
     <s v="Rafaela Silva"/>
     <x v="2"/>
-    <d v="2024-06-08T00:00:00"/>
+    <x v="102"/>
     <x v="1"/>
     <n v="10"/>
     <s v="Quarterly"/>
@@ -7303,7 +8275,7 @@
     <n v="3335"/>
     <s v="Samantha Moraes"/>
     <x v="1"/>
-    <d v="2024-06-09T00:00:00"/>
+    <x v="103"/>
     <x v="0"/>
     <n v="5"/>
     <s v="Monthly"/>
@@ -7318,7 +8290,7 @@
     <n v="3336"/>
     <s v="Tatiana Rocha"/>
     <x v="1"/>
-    <d v="2024-06-10T00:00:00"/>
+    <x v="104"/>
     <x v="0"/>
     <n v="5"/>
     <s v="Monthly"/>
@@ -7333,7 +8305,7 @@
     <n v="3337"/>
     <s v="Ulisses Tavares"/>
     <x v="0"/>
-    <d v="2024-06-11T00:00:00"/>
+    <x v="105"/>
     <x v="1"/>
     <n v="15"/>
     <s v="Quarterly"/>
@@ -7348,7 +8320,7 @@
     <n v="3338"/>
     <s v="Víctor Lemos"/>
     <x v="2"/>
-    <d v="2024-06-12T00:00:00"/>
+    <x v="106"/>
     <x v="0"/>
     <n v="10"/>
     <s v="Annual"/>
@@ -7363,7 +8335,7 @@
     <n v="3339"/>
     <s v="Wilma Barros"/>
     <x v="1"/>
-    <d v="2024-06-13T00:00:00"/>
+    <x v="107"/>
     <x v="1"/>
     <n v="5"/>
     <s v="Quarterly"/>
@@ -7378,7 +8350,7 @@
     <n v="3340"/>
     <s v="Xavier Nascimento"/>
     <x v="0"/>
-    <d v="2024-06-14T00:00:00"/>
+    <x v="108"/>
     <x v="0"/>
     <n v="15"/>
     <s v="Monthly"/>
@@ -7393,7 +8365,7 @@
     <n v="3341"/>
     <s v="Yago Pereira"/>
     <x v="2"/>
-    <d v="2024-06-15T00:00:00"/>
+    <x v="109"/>
     <x v="1"/>
     <n v="10"/>
     <s v="Monthly"/>
@@ -7408,7 +8380,7 @@
     <n v="3342"/>
     <s v="Zilda Ferreira"/>
     <x v="1"/>
-    <d v="2024-06-16T00:00:00"/>
+    <x v="110"/>
     <x v="0"/>
     <n v="5"/>
     <s v="Annual"/>
@@ -7423,7 +8395,7 @@
     <n v="3343"/>
     <s v="Amanda Lopes"/>
     <x v="0"/>
-    <d v="2024-06-17T00:00:00"/>
+    <x v="111"/>
     <x v="1"/>
     <n v="15"/>
     <s v="Quarterly"/>
@@ -7438,7 +8410,7 @@
     <n v="3344"/>
     <s v="Bruno Miranda"/>
     <x v="2"/>
-    <d v="2024-06-18T00:00:00"/>
+    <x v="112"/>
     <x v="0"/>
     <n v="10"/>
     <s v="Quarterly"/>
@@ -7453,7 +8425,7 @@
     <n v="3345"/>
     <s v="Célia Torres"/>
     <x v="1"/>
-    <d v="2024-06-19T00:00:00"/>
+    <x v="113"/>
     <x v="1"/>
     <n v="5"/>
     <s v="Monthly"/>
@@ -7468,7 +8440,7 @@
     <n v="3346"/>
     <s v="Diogo Souza"/>
     <x v="0"/>
-    <d v="2024-06-20T00:00:00"/>
+    <x v="114"/>
     <x v="0"/>
     <n v="15"/>
     <s v="Annual"/>
@@ -7483,7 +8455,7 @@
     <n v="3347"/>
     <s v="Elisa Castro"/>
     <x v="2"/>
-    <d v="2024-06-21T00:00:00"/>
+    <x v="115"/>
     <x v="1"/>
     <n v="10"/>
     <s v="Monthly"/>
@@ -7498,7 +8470,7 @@
     <n v="3348"/>
     <s v="Fátima Lima"/>
     <x v="1"/>
-    <d v="2024-06-22T00:00:00"/>
+    <x v="116"/>
     <x v="0"/>
     <n v="5"/>
     <s v="Quarterly"/>
@@ -7513,7 +8485,7 @@
     <n v="3349"/>
     <s v="Geraldo Ribeiro"/>
     <x v="0"/>
-    <d v="2024-06-23T00:00:00"/>
+    <x v="117"/>
     <x v="1"/>
     <n v="15"/>
     <s v="Monthly"/>
@@ -7528,7 +8500,7 @@
     <n v="3350"/>
     <s v="Hélio Martins"/>
     <x v="2"/>
-    <d v="2024-06-24T00:00:00"/>
+    <x v="118"/>
     <x v="0"/>
     <n v="10"/>
     <s v="Annual"/>
@@ -7543,7 +8515,7 @@
     <n v="3351"/>
     <s v="Íris Santos"/>
     <x v="1"/>
-    <d v="2024-06-25T00:00:00"/>
+    <x v="119"/>
     <x v="1"/>
     <n v="5"/>
     <s v="Monthly"/>
@@ -7558,7 +8530,7 @@
     <n v="3352"/>
     <s v="João Marcelo"/>
     <x v="0"/>
-    <d v="2024-06-26T00:00:00"/>
+    <x v="120"/>
     <x v="0"/>
     <n v="15"/>
     <s v="Quarterly"/>
@@ -7573,7 +8545,7 @@
     <n v="3353"/>
     <s v="Larissa Gomes"/>
     <x v="2"/>
-    <d v="2024-06-27T00:00:00"/>
+    <x v="121"/>
     <x v="1"/>
     <n v="10"/>
     <s v="Monthly"/>
@@ -7588,7 +8560,7 @@
     <n v="3354"/>
     <s v="Márcio Silva"/>
     <x v="1"/>
-    <d v="2024-06-28T00:00:00"/>
+    <x v="122"/>
     <x v="0"/>
     <n v="5"/>
     <s v="Annual"/>
@@ -7603,7 +8575,7 @@
     <n v="3355"/>
     <s v="Nadia Costa"/>
     <x v="0"/>
-    <d v="2024-06-29T00:00:00"/>
+    <x v="123"/>
     <x v="1"/>
     <n v="15"/>
     <s v="Monthly"/>
@@ -7618,7 +8590,7 @@
     <n v="3356"/>
     <s v="Oscar Almeida"/>
     <x v="2"/>
-    <d v="2024-06-30T00:00:00"/>
+    <x v="124"/>
     <x v="0"/>
     <n v="10"/>
     <s v="Quarterly"/>
@@ -7633,7 +8605,7 @@
     <n v="3357"/>
     <s v="Patricia Soares"/>
     <x v="1"/>
-    <d v="2024-07-01T00:00:00"/>
+    <x v="125"/>
     <x v="1"/>
     <n v="5"/>
     <s v="Monthly"/>
@@ -7648,7 +8620,7 @@
     <n v="3358"/>
     <s v="Quênia Barros"/>
     <x v="0"/>
-    <d v="2024-07-02T00:00:00"/>
+    <x v="126"/>
     <x v="0"/>
     <n v="15"/>
     <s v="Annual"/>
@@ -7663,7 +8635,7 @@
     <n v="3359"/>
     <s v="Rafael Torres"/>
     <x v="2"/>
-    <d v="2024-07-03T00:00:00"/>
+    <x v="127"/>
     <x v="1"/>
     <n v="10"/>
     <s v="Monthly"/>
@@ -7678,7 +8650,7 @@
     <n v="3360"/>
     <s v="Silvia Nascimento"/>
     <x v="1"/>
-    <d v="2024-07-04T00:00:00"/>
+    <x v="128"/>
     <x v="0"/>
     <n v="5"/>
     <s v="Quarterly"/>
@@ -7693,7 +8665,7 @@
     <n v="3361"/>
     <s v="Tiago Mendes"/>
     <x v="0"/>
-    <d v="2024-07-05T00:00:00"/>
+    <x v="129"/>
     <x v="1"/>
     <n v="15"/>
     <s v="Monthly"/>
@@ -7708,7 +8680,7 @@
     <n v="3362"/>
     <s v="Ursula Silva"/>
     <x v="2"/>
-    <d v="2024-07-06T00:00:00"/>
+    <x v="130"/>
     <x v="0"/>
     <n v="10"/>
     <s v="Annual"/>
@@ -7723,7 +8695,7 @@
     <n v="3363"/>
     <s v="Vanessa Moraes"/>
     <x v="1"/>
-    <d v="2024-07-07T00:00:00"/>
+    <x v="131"/>
     <x v="1"/>
     <n v="5"/>
     <s v="Monthly"/>
@@ -7738,7 +8710,7 @@
     <n v="3364"/>
     <s v="Waldir Junior"/>
     <x v="0"/>
-    <d v="2024-07-08T00:00:00"/>
+    <x v="132"/>
     <x v="0"/>
     <n v="15"/>
     <s v="Quarterly"/>
@@ -7753,7 +8725,7 @@
     <n v="3365"/>
     <s v="Xavier Lopes"/>
     <x v="2"/>
-    <d v="2024-07-09T00:00:00"/>
+    <x v="133"/>
     <x v="1"/>
     <n v="10"/>
     <s v="Monthly"/>
@@ -7768,7 +8740,7 @@
     <n v="3366"/>
     <s v="Yolanda Freitas"/>
     <x v="1"/>
-    <d v="2024-07-10T00:00:00"/>
+    <x v="134"/>
     <x v="0"/>
     <n v="5"/>
     <s v="Monthly"/>
@@ -7783,7 +8755,7 @@
     <n v="3367"/>
     <s v="Zacarias Nunes"/>
     <x v="0"/>
-    <d v="2024-07-11T00:00:00"/>
+    <x v="135"/>
     <x v="1"/>
     <n v="15"/>
     <s v="Quarterly"/>
@@ -7798,7 +8770,7 @@
     <n v="3368"/>
     <s v="Ana Clara Barreto"/>
     <x v="2"/>
-    <d v="2024-07-12T00:00:00"/>
+    <x v="136"/>
     <x v="0"/>
     <n v="10"/>
     <s v="Annual"/>
@@ -7813,7 +8785,7 @@
     <n v="3369"/>
     <s v="Bruno Henrique"/>
     <x v="1"/>
-    <d v="2024-07-13T00:00:00"/>
+    <x v="137"/>
     <x v="1"/>
     <n v="5"/>
     <s v="Quarterly"/>
@@ -7828,7 +8800,7 @@
     <n v="3370"/>
     <s v="Carlos Eduardo"/>
     <x v="0"/>
-    <d v="2024-07-14T00:00:00"/>
+    <x v="138"/>
     <x v="0"/>
     <n v="15"/>
     <s v="Monthly"/>
@@ -7843,7 +8815,7 @@
     <n v="3371"/>
     <s v="Débora Lima"/>
     <x v="2"/>
-    <d v="2024-07-15T00:00:00"/>
+    <x v="139"/>
     <x v="1"/>
     <n v="10"/>
     <s v="Monthly"/>
@@ -7858,7 +8830,7 @@
     <n v="3372"/>
     <s v="Elisa Neves"/>
     <x v="1"/>
-    <d v="2024-07-16T00:00:00"/>
+    <x v="140"/>
     <x v="0"/>
     <n v="5"/>
     <s v="Annual"/>
@@ -7873,7 +8845,7 @@
     <n v="3373"/>
     <s v="Fabiano Gomes"/>
     <x v="0"/>
-    <d v="2024-07-17T00:00:00"/>
+    <x v="141"/>
     <x v="1"/>
     <n v="15"/>
     <s v="Quarterly"/>
@@ -7888,7 +8860,7 @@
     <n v="3374"/>
     <s v="Gisele Oliveira"/>
     <x v="2"/>
-    <d v="2024-07-18T00:00:00"/>
+    <x v="142"/>
     <x v="0"/>
     <n v="10"/>
     <s v="Quarterly"/>
@@ -7903,7 +8875,7 @@
     <n v="3375"/>
     <s v="Héctor Silva"/>
     <x v="1"/>
-    <d v="2024-07-19T00:00:00"/>
+    <x v="143"/>
     <x v="1"/>
     <n v="5"/>
     <s v="Monthly"/>
@@ -7918,7 +8890,7 @@
     <n v="3376"/>
     <s v="Igor Martins"/>
     <x v="0"/>
-    <d v="2024-07-20T00:00:00"/>
+    <x v="144"/>
     <x v="0"/>
     <n v="15"/>
     <s v="Annual"/>
@@ -7933,7 +8905,7 @@
     <n v="3377"/>
     <s v="Joana Figueiredo"/>
     <x v="2"/>
-    <d v="2024-07-21T00:00:00"/>
+    <x v="145"/>
     <x v="1"/>
     <n v="10"/>
     <s v="Monthly"/>
@@ -7948,7 +8920,7 @@
     <n v="3378"/>
     <s v="Kleber Machado"/>
     <x v="1"/>
-    <d v="2024-07-22T00:00:00"/>
+    <x v="146"/>
     <x v="0"/>
     <n v="5"/>
     <s v="Quarterly"/>
@@ -7963,7 +8935,7 @@
     <n v="3379"/>
     <s v="Luciana Santos"/>
     <x v="0"/>
-    <d v="2024-07-23T00:00:00"/>
+    <x v="147"/>
     <x v="1"/>
     <n v="15"/>
     <s v="Monthly"/>
@@ -7978,7 +8950,7 @@
     <n v="3380"/>
     <s v="Marcos Teixeira"/>
     <x v="2"/>
-    <d v="2024-07-24T00:00:00"/>
+    <x v="148"/>
     <x v="0"/>
     <n v="10"/>
     <s v="Annual"/>
@@ -7993,7 +8965,7 @@
     <n v="3381"/>
     <s v="Natalia Costa"/>
     <x v="1"/>
-    <d v="2024-07-25T00:00:00"/>
+    <x v="149"/>
     <x v="1"/>
     <n v="5"/>
     <s v="Monthly"/>
@@ -8008,7 +8980,7 @@
     <n v="3382"/>
     <s v="Oscar Ribeiro"/>
     <x v="0"/>
-    <d v="2024-07-26T00:00:00"/>
+    <x v="150"/>
     <x v="0"/>
     <n v="15"/>
     <s v="Quarterly"/>
@@ -8023,7 +8995,7 @@
     <n v="3383"/>
     <s v="Patricia Almeida"/>
     <x v="2"/>
-    <d v="2024-07-27T00:00:00"/>
+    <x v="151"/>
     <x v="1"/>
     <n v="10"/>
     <s v="Monthly"/>
@@ -8038,7 +9010,7 @@
     <n v="3384"/>
     <s v="Quirino Junior"/>
     <x v="1"/>
-    <d v="2024-07-28T00:00:00"/>
+    <x v="152"/>
     <x v="0"/>
     <n v="5"/>
     <s v="Annual"/>
@@ -8053,7 +9025,7 @@
     <n v="3385"/>
     <s v="Renata Machado"/>
     <x v="0"/>
-    <d v="2024-07-29T00:00:00"/>
+    <x v="153"/>
     <x v="1"/>
     <n v="15"/>
     <s v="Monthly"/>
@@ -8068,7 +9040,7 @@
     <n v="3386"/>
     <s v="Sônia Alves"/>
     <x v="2"/>
-    <d v="2024-07-30T00:00:00"/>
+    <x v="154"/>
     <x v="0"/>
     <n v="10"/>
     <s v="Quarterly"/>
@@ -8083,7 +9055,7 @@
     <n v="3387"/>
     <s v="Tiago Nunes"/>
     <x v="1"/>
-    <d v="2024-07-31T00:00:00"/>
+    <x v="155"/>
     <x v="1"/>
     <n v="5"/>
     <s v="Monthly"/>
@@ -8098,7 +9070,7 @@
     <n v="3388"/>
     <s v="Ulysses Pereira"/>
     <x v="0"/>
-    <d v="2024-08-01T00:00:00"/>
+    <x v="156"/>
     <x v="0"/>
     <n v="15"/>
     <s v="Annual"/>
@@ -8113,7 +9085,7 @@
     <n v="3389"/>
     <s v="Vanessa Lima"/>
     <x v="2"/>
-    <d v="2024-08-02T00:00:00"/>
+    <x v="157"/>
     <x v="1"/>
     <n v="10"/>
     <s v="Monthly"/>
@@ -8128,7 +9100,7 @@
     <n v="3390"/>
     <s v="Wagner Santos"/>
     <x v="1"/>
-    <d v="2024-08-03T00:00:00"/>
+    <x v="158"/>
     <x v="0"/>
     <n v="5"/>
     <s v="Quarterly"/>
@@ -8143,7 +9115,7 @@
     <n v="3391"/>
     <s v="Xuxa Meneghel"/>
     <x v="0"/>
-    <d v="2024-08-04T00:00:00"/>
+    <x v="159"/>
     <x v="1"/>
     <n v="15"/>
     <s v="Monthly"/>
@@ -8158,7 +9130,7 @@
     <n v="3392"/>
     <s v="Yasmin Silva"/>
     <x v="2"/>
-    <d v="2024-08-05T00:00:00"/>
+    <x v="160"/>
     <x v="0"/>
     <n v="10"/>
     <s v="Annual"/>
@@ -8173,7 +9145,7 @@
     <n v="3393"/>
     <s v="Zacarias de Souza"/>
     <x v="1"/>
-    <d v="2024-08-06T00:00:00"/>
+    <x v="161"/>
     <x v="1"/>
     <n v="5"/>
     <s v="Monthly"/>
@@ -8188,7 +9160,7 @@
     <n v="3394"/>
     <s v="André Lima"/>
     <x v="0"/>
-    <d v="2024-08-07T00:00:00"/>
+    <x v="162"/>
     <x v="0"/>
     <n v="15"/>
     <s v="Quarterly"/>
@@ -8203,7 +9175,7 @@
     <n v="3395"/>
     <s v="Bianca Freitas"/>
     <x v="2"/>
-    <d v="2024-08-08T00:00:00"/>
+    <x v="163"/>
     <x v="1"/>
     <n v="10"/>
     <s v="Monthly"/>
@@ -8218,7 +9190,7 @@
     <n v="3396"/>
     <s v="Caio Mendes"/>
     <x v="1"/>
-    <d v="2024-08-09T00:00:00"/>
+    <x v="164"/>
     <x v="0"/>
     <n v="5"/>
     <s v="Annual"/>
@@ -8233,7 +9205,7 @@
     <n v="3397"/>
     <s v="Daniela Moura"/>
     <x v="0"/>
-    <d v="2024-08-10T00:00:00"/>
+    <x v="165"/>
     <x v="1"/>
     <n v="15"/>
     <s v="Monthly"/>
@@ -8248,7 +9220,7 @@
     <n v="3398"/>
     <s v="Eduardo Costa"/>
     <x v="2"/>
-    <d v="2024-08-11T00:00:00"/>
+    <x v="166"/>
     <x v="0"/>
     <n v="10"/>
     <s v="Quarterly"/>
@@ -8263,7 +9235,7 @@
     <n v="3399"/>
     <s v="Fernanda Gomes"/>
     <x v="1"/>
-    <d v="2024-08-12T00:00:00"/>
+    <x v="167"/>
     <x v="1"/>
     <n v="5"/>
     <s v="Monthly"/>
@@ -8278,7 +9250,7 @@
     <n v="3400"/>
     <s v="Guilherme Souza"/>
     <x v="0"/>
-    <d v="2024-08-13T00:00:00"/>
+    <x v="168"/>
     <x v="0"/>
     <n v="15"/>
     <s v="Annual"/>
@@ -8293,7 +9265,7 @@
     <n v="3401"/>
     <s v="Helena Ribeiro"/>
     <x v="2"/>
-    <d v="2024-08-14T00:00:00"/>
+    <x v="169"/>
     <x v="1"/>
     <n v="10"/>
     <s v="Monthly"/>
@@ -8308,7 +9280,7 @@
     <n v="3402"/>
     <s v="Igor Santos"/>
     <x v="1"/>
-    <d v="2024-08-15T00:00:00"/>
+    <x v="170"/>
     <x v="0"/>
     <n v="5"/>
     <s v="Quarterly"/>
@@ -8323,7 +9295,7 @@
     <n v="3403"/>
     <s v="João Carvalho"/>
     <x v="0"/>
-    <d v="2024-08-16T00:00:00"/>
+    <x v="171"/>
     <x v="1"/>
     <n v="15"/>
     <s v="Monthly"/>
@@ -8338,7 +9310,7 @@
     <n v="3404"/>
     <s v="Klara Fagundes"/>
     <x v="2"/>
-    <d v="2024-08-17T00:00:00"/>
+    <x v="172"/>
     <x v="0"/>
     <n v="10"/>
     <s v="Annual"/>
@@ -8353,7 +9325,7 @@
     <n v="3405"/>
     <s v="Lúcia Mendonça"/>
     <x v="1"/>
-    <d v="2024-08-18T00:00:00"/>
+    <x v="173"/>
     <x v="1"/>
     <n v="5"/>
     <s v="Monthly"/>
@@ -8368,7 +9340,7 @@
     <n v="3406"/>
     <s v="Marcelo Novaes"/>
     <x v="1"/>
-    <d v="2024-08-19T00:00:00"/>
+    <x v="174"/>
     <x v="0"/>
     <n v="5"/>
     <s v="Monthly"/>
@@ -8383,7 +9355,7 @@
     <n v="3407"/>
     <s v="Nina Pacheco"/>
     <x v="0"/>
-    <d v="2024-08-20T00:00:00"/>
+    <x v="175"/>
     <x v="1"/>
     <n v="15"/>
     <s v="Quarterly"/>
@@ -8398,7 +9370,7 @@
     <n v="3408"/>
     <s v="Olívia Rios"/>
     <x v="2"/>
-    <d v="2024-08-21T00:00:00"/>
+    <x v="176"/>
     <x v="0"/>
     <n v="10"/>
     <s v="Annual"/>
@@ -8413,7 +9385,7 @@
     <n v="3409"/>
     <s v="Paulo Quintana"/>
     <x v="1"/>
-    <d v="2024-08-22T00:00:00"/>
+    <x v="177"/>
     <x v="1"/>
     <n v="5"/>
     <s v="Quarterly"/>
@@ -8428,7 +9400,7 @@
     <n v="3410"/>
     <s v="Raquel Domingos"/>
     <x v="0"/>
-    <d v="2024-08-23T00:00:00"/>
+    <x v="178"/>
     <x v="0"/>
     <n v="15"/>
     <s v="Monthly"/>
@@ -8443,7 +9415,7 @@
     <n v="3411"/>
     <s v="Samuel Viana"/>
     <x v="2"/>
-    <d v="2024-08-24T00:00:00"/>
+    <x v="179"/>
     <x v="1"/>
     <n v="10"/>
     <s v="Monthly"/>
@@ -8458,7 +9430,7 @@
     <n v="3412"/>
     <s v="Tatiane Rocha"/>
     <x v="1"/>
-    <d v="2024-08-25T00:00:00"/>
+    <x v="180"/>
     <x v="0"/>
     <n v="5"/>
     <s v="Annual"/>
@@ -8473,7 +9445,7 @@
     <n v="3413"/>
     <s v="Ulysses Farias"/>
     <x v="0"/>
-    <d v="2024-08-26T00:00:00"/>
+    <x v="181"/>
     <x v="1"/>
     <n v="15"/>
     <s v="Quarterly"/>
@@ -8488,7 +9460,7 @@
     <n v="3414"/>
     <s v="Vanessa Moreira"/>
     <x v="2"/>
-    <d v="2024-08-27T00:00:00"/>
+    <x v="182"/>
     <x v="0"/>
     <n v="10"/>
     <s v="Quarterly"/>
@@ -8503,7 +9475,7 @@
     <n v="3415"/>
     <s v="William Carvalho"/>
     <x v="1"/>
-    <d v="2024-08-28T00:00:00"/>
+    <x v="183"/>
     <x v="1"/>
     <n v="5"/>
     <s v="Monthly"/>
@@ -8518,7 +9490,7 @@
     <n v="3416"/>
     <s v="Ximena Barros"/>
     <x v="0"/>
-    <d v="2024-08-29T00:00:00"/>
+    <x v="184"/>
     <x v="0"/>
     <n v="15"/>
     <s v="Annual"/>
@@ -8533,7 +9505,7 @@
     <n v="3417"/>
     <s v="Yara Machado"/>
     <x v="2"/>
-    <d v="2024-08-30T00:00:00"/>
+    <x v="185"/>
     <x v="1"/>
     <n v="10"/>
     <s v="Monthly"/>
@@ -8548,7 +9520,7 @@
     <n v="3418"/>
     <s v="Zacarias Costa"/>
     <x v="1"/>
-    <d v="2024-08-31T00:00:00"/>
+    <x v="186"/>
     <x v="0"/>
     <n v="5"/>
     <s v="Quarterly"/>
@@ -8563,7 +9535,7 @@
     <n v="3419"/>
     <s v="André Lopes"/>
     <x v="0"/>
-    <d v="2024-09-01T00:00:00"/>
+    <x v="187"/>
     <x v="1"/>
     <n v="15"/>
     <s v="Monthly"/>
@@ -8578,7 +9550,7 @@
     <n v="3420"/>
     <s v="Beatriz Souza"/>
     <x v="2"/>
-    <d v="2024-09-02T00:00:00"/>
+    <x v="188"/>
     <x v="0"/>
     <n v="10"/>
     <s v="Annual"/>
@@ -8593,7 +9565,7 @@
     <n v="3421"/>
     <s v="Caio Pereira"/>
     <x v="1"/>
-    <d v="2024-09-03T00:00:00"/>
+    <x v="189"/>
     <x v="1"/>
     <n v="5"/>
     <s v="Monthly"/>
@@ -8608,7 +9580,7 @@
     <n v="3422"/>
     <s v="Daniela Araújo"/>
     <x v="0"/>
-    <d v="2024-09-04T00:00:00"/>
+    <x v="190"/>
     <x v="0"/>
     <n v="15"/>
     <s v="Quarterly"/>
@@ -8623,7 +9595,7 @@
     <n v="3423"/>
     <s v="Eduardo Santos"/>
     <x v="2"/>
-    <d v="2024-09-05T00:00:00"/>
+    <x v="191"/>
     <x v="1"/>
     <n v="10"/>
     <s v="Monthly"/>
@@ -8638,7 +9610,7 @@
     <n v="3424"/>
     <s v="Fernanda Lima"/>
     <x v="1"/>
-    <d v="2024-09-06T00:00:00"/>
+    <x v="192"/>
     <x v="0"/>
     <n v="5"/>
     <s v="Annual"/>
@@ -8653,7 +9625,7 @@
     <n v="3425"/>
     <s v="Gabriel Teixeira"/>
     <x v="0"/>
-    <d v="2024-09-07T00:00:00"/>
+    <x v="193"/>
     <x v="1"/>
     <n v="15"/>
     <s v="Monthly"/>
@@ -8668,7 +9640,7 @@
     <n v="3426"/>
     <s v="Helena Ribeiro"/>
     <x v="2"/>
-    <d v="2024-09-08T00:00:00"/>
+    <x v="194"/>
     <x v="0"/>
     <n v="10"/>
     <s v="Quarterly"/>
@@ -8683,7 +9655,7 @@
     <n v="3427"/>
     <s v="Igor Mendes"/>
     <x v="1"/>
-    <d v="2024-09-09T00:00:00"/>
+    <x v="195"/>
     <x v="1"/>
     <n v="5"/>
     <s v="Monthly"/>
@@ -8698,7 +9670,7 @@
     <n v="3428"/>
     <s v="Joana Silveira"/>
     <x v="0"/>
-    <d v="2024-09-10T00:00:00"/>
+    <x v="196"/>
     <x v="0"/>
     <n v="15"/>
     <s v="Annual"/>
@@ -8713,7 +9685,7 @@
     <n v="3429"/>
     <s v="Lucas Martins"/>
     <x v="2"/>
-    <d v="2024-09-11T00:00:00"/>
+    <x v="197"/>
     <x v="1"/>
     <n v="10"/>
     <s v="Monthly"/>
@@ -8728,7 +9700,7 @@
     <n v="3430"/>
     <s v="Marcela Gouveia"/>
     <x v="1"/>
-    <d v="2024-09-12T00:00:00"/>
+    <x v="198"/>
     <x v="0"/>
     <n v="5"/>
     <s v="Quarterly"/>
@@ -8743,7 +9715,7 @@
     <n v="3431"/>
     <s v="Nicolas Borges"/>
     <x v="0"/>
-    <d v="2024-09-13T00:00:00"/>
+    <x v="199"/>
     <x v="1"/>
     <n v="15"/>
     <s v="Monthly"/>
@@ -8758,7 +9730,7 @@
     <n v="3432"/>
     <s v="Olivia Freitas"/>
     <x v="2"/>
-    <d v="2024-09-14T00:00:00"/>
+    <x v="200"/>
     <x v="0"/>
     <n v="10"/>
     <s v="Annual"/>
@@ -8773,7 +9745,7 @@
     <n v="3433"/>
     <s v="Paulo Nogueira"/>
     <x v="1"/>
-    <d v="2024-09-15T00:00:00"/>
+    <x v="201"/>
     <x v="1"/>
     <n v="5"/>
     <s v="Monthly"/>
@@ -8788,7 +9760,7 @@
     <n v="3434"/>
     <s v="Raquel Andrade"/>
     <x v="0"/>
-    <d v="2024-09-16T00:00:00"/>
+    <x v="202"/>
     <x v="0"/>
     <n v="15"/>
     <s v="Quarterly"/>
@@ -8803,7 +9775,7 @@
     <n v="3435"/>
     <s v="Sônia Carvalho"/>
     <x v="2"/>
-    <d v="2024-09-17T00:00:00"/>
+    <x v="203"/>
     <x v="1"/>
     <n v="10"/>
     <s v="Monthly"/>
@@ -8818,7 +9790,7 @@
     <n v="3436"/>
     <s v="Tiago Rodrigues"/>
     <x v="1"/>
-    <d v="2024-09-18T00:00:00"/>
+    <x v="204"/>
     <x v="0"/>
     <n v="5"/>
     <s v="Monthly"/>
@@ -8833,7 +9805,7 @@
     <n v="3437"/>
     <s v="Ursula Monteiro"/>
     <x v="0"/>
-    <d v="2024-09-19T00:00:00"/>
+    <x v="205"/>
     <x v="1"/>
     <n v="15"/>
     <s v="Quarterly"/>
@@ -8848,7 +9820,7 @@
     <n v="3438"/>
     <s v="Vanessa Pereira"/>
     <x v="2"/>
-    <d v="2024-09-20T00:00:00"/>
+    <x v="206"/>
     <x v="0"/>
     <n v="10"/>
     <s v="Annual"/>
@@ -8863,7 +9835,7 @@
     <n v="3439"/>
     <s v="Walter Silva"/>
     <x v="1"/>
-    <d v="2024-09-21T00:00:00"/>
+    <x v="207"/>
     <x v="1"/>
     <n v="5"/>
     <s v="Quarterly"/>
@@ -8878,7 +9850,7 @@
     <n v="3440"/>
     <s v="Xavier Almeida"/>
     <x v="0"/>
-    <d v="2024-09-22T00:00:00"/>
+    <x v="208"/>
     <x v="0"/>
     <n v="15"/>
     <s v="Monthly"/>
@@ -8893,7 +9865,7 @@
     <n v="3441"/>
     <s v="Yasmine Correia"/>
     <x v="2"/>
-    <d v="2024-09-23T00:00:00"/>
+    <x v="209"/>
     <x v="1"/>
     <n v="10"/>
     <s v="Monthly"/>
@@ -8908,7 +9880,7 @@
     <n v="3442"/>
     <s v="Zacarias Almeida"/>
     <x v="1"/>
-    <d v="2024-09-24T00:00:00"/>
+    <x v="210"/>
     <x v="0"/>
     <n v="5"/>
     <s v="Annual"/>
@@ -8923,7 +9895,7 @@
     <n v="3443"/>
     <s v="Amanda Costa"/>
     <x v="0"/>
-    <d v="2024-09-25T00:00:00"/>
+    <x v="211"/>
     <x v="1"/>
     <n v="15"/>
     <s v="Quarterly"/>
@@ -8938,7 +9910,7 @@
     <n v="3444"/>
     <s v="Bruno Ferreira"/>
     <x v="2"/>
-    <d v="2024-09-26T00:00:00"/>
+    <x v="212"/>
     <x v="0"/>
     <n v="10"/>
     <s v="Quarterly"/>
@@ -8953,7 +9925,7 @@
     <n v="3445"/>
     <s v="Carla Dias"/>
     <x v="1"/>
-    <d v="2024-09-27T00:00:00"/>
+    <x v="213"/>
     <x v="1"/>
     <n v="5"/>
     <s v="Monthly"/>
@@ -8968,7 +9940,7 @@
     <n v="3446"/>
     <s v="Diogo Martins"/>
     <x v="0"/>
-    <d v="2024-09-28T00:00:00"/>
+    <x v="214"/>
     <x v="0"/>
     <n v="15"/>
     <s v="Annual"/>
@@ -8983,7 +9955,7 @@
     <n v="3447"/>
     <s v="Elisa Campos"/>
     <x v="2"/>
-    <d v="2024-09-29T00:00:00"/>
+    <x v="215"/>
     <x v="1"/>
     <n v="10"/>
     <s v="Monthly"/>
@@ -8998,7 +9970,7 @@
     <n v="3448"/>
     <s v="Fabiana Lima"/>
     <x v="1"/>
-    <d v="2024-09-30T00:00:00"/>
+    <x v="216"/>
     <x v="0"/>
     <n v="5"/>
     <s v="Quarterly"/>
@@ -9013,7 +9985,7 @@
     <n v="3449"/>
     <s v="Gabriel Santos"/>
     <x v="0"/>
-    <d v="2024-10-01T00:00:00"/>
+    <x v="217"/>
     <x v="1"/>
     <n v="15"/>
     <s v="Monthly"/>
@@ -9028,7 +10000,7 @@
     <n v="3450"/>
     <s v="Helena Ferreira"/>
     <x v="2"/>
-    <d v="2024-10-02T00:00:00"/>
+    <x v="218"/>
     <x v="0"/>
     <n v="10"/>
     <s v="Annual"/>
@@ -9043,7 +10015,7 @@
     <n v="3451"/>
     <s v="Ígor Nunes"/>
     <x v="1"/>
-    <d v="2024-10-03T00:00:00"/>
+    <x v="219"/>
     <x v="1"/>
     <n v="5"/>
     <s v="Monthly"/>
@@ -9058,7 +10030,7 @@
     <n v="3452"/>
     <s v="Joana Silveira"/>
     <x v="0"/>
-    <d v="2024-10-04T00:00:00"/>
+    <x v="220"/>
     <x v="0"/>
     <n v="15"/>
     <s v="Quarterly"/>
@@ -9073,7 +10045,7 @@
     <n v="3453"/>
     <s v="Kléber Oliveira"/>
     <x v="2"/>
-    <d v="2024-10-05T00:00:00"/>
+    <x v="221"/>
     <x v="1"/>
     <n v="10"/>
     <s v="Monthly"/>
@@ -9088,7 +10060,7 @@
     <n v="3454"/>
     <s v="Luciana Morais"/>
     <x v="1"/>
-    <d v="2024-10-06T00:00:00"/>
+    <x v="222"/>
     <x v="0"/>
     <n v="5"/>
     <s v="Annual"/>
@@ -9103,7 +10075,7 @@
     <n v="3455"/>
     <s v="Marcos Vinícius"/>
     <x v="0"/>
-    <d v="2024-10-07T00:00:00"/>
+    <x v="223"/>
     <x v="1"/>
     <n v="15"/>
     <s v="Monthly"/>
@@ -9118,7 +10090,7 @@
     <n v="3456"/>
     <s v="Natália Barros"/>
     <x v="2"/>
-    <d v="2024-10-08T00:00:00"/>
+    <x v="224"/>
     <x v="0"/>
     <n v="10"/>
     <s v="Quarterly"/>
@@ -9133,7 +10105,7 @@
     <n v="3457"/>
     <s v="Oscar Sampaio"/>
     <x v="1"/>
-    <d v="2024-10-09T00:00:00"/>
+    <x v="225"/>
     <x v="1"/>
     <n v="5"/>
     <s v="Monthly"/>
@@ -9148,7 +10120,7 @@
     <n v="3458"/>
     <s v="Patrícia Leite"/>
     <x v="0"/>
-    <d v="2024-10-10T00:00:00"/>
+    <x v="226"/>
     <x v="0"/>
     <n v="15"/>
     <s v="Annual"/>
@@ -9163,7 +10135,7 @@
     <n v="3459"/>
     <s v="Quênia Rocha"/>
     <x v="2"/>
-    <d v="2024-10-11T00:00:00"/>
+    <x v="227"/>
     <x v="1"/>
     <n v="10"/>
     <s v="Monthly"/>
@@ -9178,7 +10150,7 @@
     <n v="3460"/>
     <s v="Rafael Torres"/>
     <x v="1"/>
-    <d v="2024-10-12T00:00:00"/>
+    <x v="228"/>
     <x v="0"/>
     <n v="5"/>
     <s v="Quarterly"/>
@@ -9193,7 +10165,7 @@
     <n v="3461"/>
     <s v="Sandra Gouveia"/>
     <x v="0"/>
-    <d v="2024-10-13T00:00:00"/>
+    <x v="229"/>
     <x v="1"/>
     <n v="15"/>
     <s v="Monthly"/>
@@ -9208,7 +10180,7 @@
     <n v="3462"/>
     <s v="Tiago Lacerda"/>
     <x v="2"/>
-    <d v="2024-10-14T00:00:00"/>
+    <x v="230"/>
     <x v="0"/>
     <n v="10"/>
     <s v="Annual"/>
@@ -9223,7 +10195,7 @@
     <n v="3463"/>
     <s v="Ursula Fonseca"/>
     <x v="1"/>
-    <d v="2024-10-15T00:00:00"/>
+    <x v="231"/>
     <x v="1"/>
     <n v="5"/>
     <s v="Monthly"/>
@@ -9238,7 +10210,7 @@
     <n v="3464"/>
     <s v="Vanessa Andrade"/>
     <x v="0"/>
-    <d v="2024-10-16T00:00:00"/>
+    <x v="232"/>
     <x v="0"/>
     <n v="15"/>
     <s v="Quarterly"/>
@@ -9253,7 +10225,7 @@
     <n v="3465"/>
     <s v="William Castro"/>
     <x v="2"/>
-    <d v="2024-10-17T00:00:00"/>
+    <x v="233"/>
     <x v="1"/>
     <n v="10"/>
     <s v="Monthly"/>
@@ -9268,7 +10240,7 @@
     <n v="3466"/>
     <s v="Xavier Monteiro"/>
     <x v="1"/>
-    <d v="2024-10-18T00:00:00"/>
+    <x v="234"/>
     <x v="0"/>
     <n v="5"/>
     <s v="Annual"/>
@@ -9283,7 +10255,7 @@
     <n v="3467"/>
     <s v="Yasmin Figueira"/>
     <x v="0"/>
-    <d v="2024-10-19T00:00:00"/>
+    <x v="235"/>
     <x v="1"/>
     <n v="15"/>
     <s v="Monthly"/>
@@ -9298,7 +10270,7 @@
     <n v="3468"/>
     <s v="Zacarias Mendonça"/>
     <x v="2"/>
-    <d v="2024-10-20T00:00:00"/>
+    <x v="236"/>
     <x v="0"/>
     <n v="10"/>
     <s v="Quarterly"/>
@@ -9313,7 +10285,7 @@
     <n v="3469"/>
     <s v="Amanda Menezes"/>
     <x v="1"/>
-    <d v="2024-10-21T00:00:00"/>
+    <x v="237"/>
     <x v="1"/>
     <n v="5"/>
     <s v="Monthly"/>
@@ -9328,7 +10300,7 @@
     <n v="3470"/>
     <s v="Bruno Santos"/>
     <x v="0"/>
-    <d v="2024-10-22T00:00:00"/>
+    <x v="238"/>
     <x v="0"/>
     <n v="15"/>
     <s v="Annual"/>
@@ -9343,7 +10315,7 @@
     <n v="3471"/>
     <s v="Carla Ferreira"/>
     <x v="2"/>
-    <d v="2024-10-23T00:00:00"/>
+    <x v="239"/>
     <x v="1"/>
     <n v="10"/>
     <s v="Monthly"/>
@@ -9358,7 +10330,7 @@
     <n v="3472"/>
     <s v="Diogo Alves"/>
     <x v="1"/>
-    <d v="2024-10-24T00:00:00"/>
+    <x v="240"/>
     <x v="0"/>
     <n v="5"/>
     <s v="Quarterly"/>
@@ -9373,7 +10345,7 @@
     <n v="3473"/>
     <s v="Elisa Neves"/>
     <x v="0"/>
-    <d v="2024-10-25T00:00:00"/>
+    <x v="241"/>
     <x v="1"/>
     <n v="15"/>
     <s v="Monthly"/>
@@ -9388,7 +10360,7 @@
     <n v="3474"/>
     <s v="Fabiano Pires"/>
     <x v="2"/>
-    <d v="2024-10-26T00:00:00"/>
+    <x v="242"/>
     <x v="0"/>
     <n v="10"/>
     <s v="Annual"/>
@@ -9403,7 +10375,7 @@
     <n v="3475"/>
     <s v="Giovana Ribeiro"/>
     <x v="1"/>
-    <d v="2024-10-27T00:00:00"/>
+    <x v="243"/>
     <x v="1"/>
     <n v="5"/>
     <s v="Monthly"/>
@@ -9418,7 +10390,7 @@
     <n v="3476"/>
     <s v="Hélio Costa"/>
     <x v="0"/>
-    <d v="2024-10-28T00:00:00"/>
+    <x v="244"/>
     <x v="0"/>
     <n v="15"/>
     <s v="Quarterly"/>
@@ -9433,7 +10405,7 @@
     <n v="3477"/>
     <s v="Íris Loureiro"/>
     <x v="2"/>
-    <d v="2024-10-29T00:00:00"/>
+    <x v="245"/>
     <x v="1"/>
     <n v="10"/>
     <s v="Monthly"/>
@@ -9448,7 +10420,7 @@
     <n v="3478"/>
     <s v="João Pereira"/>
     <x v="1"/>
-    <d v="2024-10-30T00:00:00"/>
+    <x v="246"/>
     <x v="0"/>
     <n v="5"/>
     <s v="Annual"/>
@@ -9463,7 +10435,7 @@
     <n v="3479"/>
     <s v="Klara Silva"/>
     <x v="0"/>
-    <d v="2024-10-31T00:00:00"/>
+    <x v="247"/>
     <x v="1"/>
     <n v="15"/>
     <s v="Monthly"/>
@@ -9478,7 +10450,7 @@
     <n v="3480"/>
     <s v="Luciana Barros"/>
     <x v="2"/>
-    <d v="2024-11-01T00:00:00"/>
+    <x v="248"/>
     <x v="0"/>
     <n v="10"/>
     <s v="Quarterly"/>
@@ -9493,7 +10465,7 @@
     <n v="3481"/>
     <s v="Marcos Gomes"/>
     <x v="1"/>
-    <d v="2024-11-02T00:00:00"/>
+    <x v="249"/>
     <x v="1"/>
     <n v="5"/>
     <s v="Monthly"/>
@@ -9508,7 +10480,7 @@
     <n v="3482"/>
     <s v="Natália Soares"/>
     <x v="0"/>
-    <d v="2024-11-03T00:00:00"/>
+    <x v="250"/>
     <x v="0"/>
     <n v="15"/>
     <s v="Annual"/>
@@ -9523,7 +10495,7 @@
     <n v="3483"/>
     <s v="Oscar Machado"/>
     <x v="2"/>
-    <d v="2024-11-04T00:00:00"/>
+    <x v="251"/>
     <x v="1"/>
     <n v="10"/>
     <s v="Monthly"/>
@@ -9538,7 +10510,7 @@
     <n v="3484"/>
     <s v="Patrícia Lima"/>
     <x v="1"/>
-    <d v="2024-11-05T00:00:00"/>
+    <x v="252"/>
     <x v="0"/>
     <n v="5"/>
     <s v="Quarterly"/>
@@ -9553,7 +10525,7 @@
     <n v="3485"/>
     <s v="Quirino Neto"/>
     <x v="0"/>
-    <d v="2024-11-06T00:00:00"/>
+    <x v="253"/>
     <x v="1"/>
     <n v="15"/>
     <s v="Monthly"/>
@@ -9568,7 +10540,7 @@
     <n v="3486"/>
     <s v="Rafaela Souza"/>
     <x v="1"/>
-    <d v="2024-11-07T00:00:00"/>
+    <x v="254"/>
     <x v="0"/>
     <n v="5"/>
     <s v="Monthly"/>
@@ -9583,7 +10555,7 @@
     <n v="3487"/>
     <s v="Sandro Almeida"/>
     <x v="0"/>
-    <d v="2024-11-08T00:00:00"/>
+    <x v="255"/>
     <x v="1"/>
     <n v="15"/>
     <s v="Quarterly"/>
@@ -9598,7 +10570,7 @@
     <n v="3488"/>
     <s v="Tânia Ribeiro"/>
     <x v="2"/>
-    <d v="2024-11-09T00:00:00"/>
+    <x v="256"/>
     <x v="0"/>
     <n v="10"/>
     <s v="Annual"/>
@@ -9613,7 +10585,7 @@
     <n v="3489"/>
     <s v="Ugo Dias"/>
     <x v="1"/>
-    <d v="2024-11-10T00:00:00"/>
+    <x v="257"/>
     <x v="1"/>
     <n v="5"/>
     <s v="Quarterly"/>
@@ -9628,7 +10600,7 @@
     <n v="3490"/>
     <s v="Valéria Lima"/>
     <x v="0"/>
-    <d v="2024-11-11T00:00:00"/>
+    <x v="258"/>
     <x v="0"/>
     <n v="15"/>
     <s v="Monthly"/>
@@ -9643,7 +10615,7 @@
     <n v="3491"/>
     <s v="William Fernandes"/>
     <x v="2"/>
-    <d v="2024-11-12T00:00:00"/>
+    <x v="259"/>
     <x v="1"/>
     <n v="10"/>
     <s v="Monthly"/>
@@ -9658,7 +10630,7 @@
     <n v="3492"/>
     <s v="Xuxa Mendes"/>
     <x v="1"/>
-    <d v="2024-11-13T00:00:00"/>
+    <x v="260"/>
     <x v="0"/>
     <n v="5"/>
     <s v="Annual"/>
@@ -9673,7 +10645,7 @@
     <n v="3493"/>
     <s v="Ygor Farias"/>
     <x v="0"/>
-    <d v="2024-11-14T00:00:00"/>
+    <x v="261"/>
     <x v="1"/>
     <n v="15"/>
     <s v="Quarterly"/>
@@ -9688,7 +10660,7 @@
     <n v="3494"/>
     <s v="Zilda Barros"/>
     <x v="2"/>
-    <d v="2024-11-15T00:00:00"/>
+    <x v="262"/>
     <x v="0"/>
     <n v="10"/>
     <s v="Quarterly"/>
@@ -9703,7 +10675,7 @@
     <n v="3495"/>
     <s v="Amanda Santos"/>
     <x v="1"/>
-    <d v="2024-11-16T00:00:00"/>
+    <x v="263"/>
     <x v="1"/>
     <n v="5"/>
     <s v="Monthly"/>
@@ -9718,7 +10690,7 @@
     <n v="3496"/>
     <s v="Bruno Costa"/>
     <x v="0"/>
-    <d v="2024-11-17T00:00:00"/>
+    <x v="264"/>
     <x v="0"/>
     <n v="15"/>
     <s v="Annual"/>
@@ -9733,7 +10705,7 @@
     <n v="3497"/>
     <s v="Carla Rodrigues"/>
     <x v="2"/>
-    <d v="2024-11-18T00:00:00"/>
+    <x v="265"/>
     <x v="1"/>
     <n v="10"/>
     <s v="Monthly"/>
@@ -9748,7 +10720,7 @@
     <n v="3498"/>
     <s v="Diogo Pereira"/>
     <x v="1"/>
-    <d v="2024-11-19T00:00:00"/>
+    <x v="266"/>
     <x v="0"/>
     <n v="5"/>
     <s v="Quarterly"/>
@@ -9763,7 +10735,7 @@
     <n v="3499"/>
     <s v="Elisa Correia"/>
     <x v="0"/>
-    <d v="2024-11-20T00:00:00"/>
+    <x v="267"/>
     <x v="1"/>
     <n v="15"/>
     <s v="Monthly"/>
@@ -9778,7 +10750,7 @@
     <n v="3500"/>
     <s v="Fábio Lourenço"/>
     <x v="2"/>
-    <d v="2024-11-21T00:00:00"/>
+    <x v="268"/>
     <x v="0"/>
     <n v="10"/>
     <s v="Annual"/>
@@ -9793,7 +10765,7 @@
     <n v="3501"/>
     <s v="Gabriela Neves"/>
     <x v="1"/>
-    <d v="2024-11-22T00:00:00"/>
+    <x v="269"/>
     <x v="1"/>
     <n v="5"/>
     <s v="Monthly"/>
@@ -9808,7 +10780,7 @@
     <n v="3502"/>
     <s v="Henrique Gonçalves"/>
     <x v="0"/>
-    <d v="2024-11-23T00:00:00"/>
+    <x v="270"/>
     <x v="0"/>
     <n v="15"/>
     <s v="Quarterly"/>
@@ -9823,7 +10795,7 @@
     <n v="3503"/>
     <s v="Íris Santos"/>
     <x v="2"/>
-    <d v="2024-11-24T00:00:00"/>
+    <x v="271"/>
     <x v="1"/>
     <n v="10"/>
     <s v="Monthly"/>
@@ -9838,7 +10810,7 @@
     <n v="3504"/>
     <s v="João Marcelo Alves"/>
     <x v="1"/>
-    <d v="2024-11-25T00:00:00"/>
+    <x v="272"/>
     <x v="0"/>
     <n v="5"/>
     <s v="Annual"/>
@@ -9853,7 +10825,7 @@
     <n v="3505"/>
     <s v="Klara Fonseca"/>
     <x v="0"/>
-    <d v="2024-11-26T00:00:00"/>
+    <x v="273"/>
     <x v="1"/>
     <n v="15"/>
     <s v="Monthly"/>
@@ -9868,7 +10840,7 @@
     <n v="3506"/>
     <s v="Lucas Mendonça"/>
     <x v="2"/>
-    <d v="2024-11-27T00:00:00"/>
+    <x v="274"/>
     <x v="0"/>
     <n v="10"/>
     <s v="Quarterly"/>
@@ -9883,7 +10855,7 @@
     <n v="3507"/>
     <s v="Marcela Torres"/>
     <x v="1"/>
-    <d v="2024-11-28T00:00:00"/>
+    <x v="275"/>
     <x v="1"/>
     <n v="5"/>
     <s v="Monthly"/>
@@ -9898,7 +10870,7 @@
     <n v="3508"/>
     <s v="Natália Castro"/>
     <x v="0"/>
-    <d v="2024-11-29T00:00:00"/>
+    <x v="276"/>
     <x v="0"/>
     <n v="15"/>
     <s v="Annual"/>
@@ -9913,7 +10885,7 @@
     <n v="3509"/>
     <s v="Oscar Martins"/>
     <x v="2"/>
-    <d v="2024-11-30T00:00:00"/>
+    <x v="277"/>
     <x v="1"/>
     <n v="10"/>
     <s v="Monthly"/>
@@ -9928,7 +10900,7 @@
     <n v="3510"/>
     <s v="Patrícia Oliveira"/>
     <x v="1"/>
-    <d v="2024-12-01T00:00:00"/>
+    <x v="278"/>
     <x v="0"/>
     <n v="5"/>
     <s v="Quarterly"/>
@@ -9943,7 +10915,7 @@
     <n v="3511"/>
     <s v="Quentin Nogueira"/>
     <x v="0"/>
-    <d v="2024-12-02T00:00:00"/>
+    <x v="279"/>
     <x v="1"/>
     <n v="15"/>
     <s v="Monthly"/>
@@ -9958,7 +10930,7 @@
     <n v="3512"/>
     <s v="Raquel Silva"/>
     <x v="2"/>
-    <d v="2024-12-03T00:00:00"/>
+    <x v="280"/>
     <x v="0"/>
     <n v="10"/>
     <s v="Annual"/>
@@ -9973,7 +10945,7 @@
     <n v="3513"/>
     <s v="Sandro Gomes"/>
     <x v="1"/>
-    <d v="2024-12-04T00:00:00"/>
+    <x v="281"/>
     <x v="1"/>
     <n v="5"/>
     <s v="Monthly"/>
@@ -9988,7 +10960,7 @@
     <n v="3514"/>
     <s v="Tânia Machado"/>
     <x v="0"/>
-    <d v="2024-12-05T00:00:00"/>
+    <x v="282"/>
     <x v="0"/>
     <n v="15"/>
     <s v="Quarterly"/>
@@ -10003,7 +10975,7 @@
     <n v="3515"/>
     <s v="Ursula Silva"/>
     <x v="2"/>
-    <d v="2024-12-06T00:00:00"/>
+    <x v="283"/>
     <x v="1"/>
     <n v="10"/>
     <s v="Monthly"/>
@@ -10018,7 +10990,7 @@
     <n v="3516"/>
     <s v="Vanessa Moraes"/>
     <x v="1"/>
-    <d v="2024-12-07T00:00:00"/>
+    <x v="284"/>
     <x v="0"/>
     <n v="5"/>
     <s v="Annual"/>
@@ -10033,7 +11005,7 @@
     <n v="3517"/>
     <s v="William Carvalho"/>
     <x v="0"/>
-    <d v="2024-12-08T00:00:00"/>
+    <x v="285"/>
     <x v="1"/>
     <n v="15"/>
     <s v="Monthly"/>
@@ -10048,7 +11020,7 @@
     <n v="3518"/>
     <s v="Xavier Reis"/>
     <x v="2"/>
-    <d v="2024-12-09T00:00:00"/>
+    <x v="286"/>
     <x v="0"/>
     <n v="10"/>
     <s v="Quarterly"/>
@@ -10063,7 +11035,7 @@
     <n v="3519"/>
     <s v="Yasmin Rocha"/>
     <x v="1"/>
-    <d v="2024-12-10T00:00:00"/>
+    <x v="287"/>
     <x v="1"/>
     <n v="5"/>
     <s v="Monthly"/>
@@ -10078,7 +11050,7 @@
     <n v="3520"/>
     <s v="Zacarias Duarte"/>
     <x v="0"/>
-    <d v="2024-12-11T00:00:00"/>
+    <x v="288"/>
     <x v="0"/>
     <n v="15"/>
     <s v="Annual"/>
@@ -10093,7 +11065,7 @@
     <n v="3521"/>
     <s v="Amanda Freitas"/>
     <x v="2"/>
-    <d v="2024-12-12T00:00:00"/>
+    <x v="289"/>
     <x v="1"/>
     <n v="10"/>
     <s v="Monthly"/>
@@ -10108,7 +11080,7 @@
     <n v="3522"/>
     <s v="Bruno Almeida"/>
     <x v="1"/>
-    <d v="2024-12-13T00:00:00"/>
+    <x v="290"/>
     <x v="0"/>
     <n v="5"/>
     <s v="Quarterly"/>
@@ -10123,7 +11095,7 @@
     <n v="3523"/>
     <s v="Carla Siqueira"/>
     <x v="0"/>
-    <d v="2024-12-14T00:00:00"/>
+    <x v="291"/>
     <x v="1"/>
     <n v="15"/>
     <s v="Monthly"/>
@@ -10138,7 +11110,7 @@
     <n v="3524"/>
     <s v="Diogo Ramos"/>
     <x v="2"/>
-    <d v="2024-12-15T00:00:00"/>
+    <x v="292"/>
     <x v="0"/>
     <n v="10"/>
     <s v="Annual"/>
@@ -10153,7 +11125,7 @@
     <n v="3525"/>
     <s v="Elisa Magalhães"/>
     <x v="1"/>
-    <d v="2024-12-16T00:00:00"/>
+    <x v="293"/>
     <x v="1"/>
     <n v="5"/>
     <s v="Monthly"/>
@@ -10168,226 +11140,7 @@
 </file>
 
 <file path=xl/pivotTables/pivotTable1.xml><?xml version="1.0" encoding="utf-8"?>
-<pivotTableDefinition xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="xr" xr:uid="{36A8AA56-C674-410D-B731-334A08BD7462}" name="Tabela dinâmica3" cacheId="4" applyNumberFormats="0" applyBorderFormats="0" applyFontFormats="0" applyPatternFormats="0" applyAlignmentFormats="0" applyWidthHeightFormats="1" dataCaption="Valores" updatedVersion="8" minRefreshableVersion="3" useAutoFormatting="1" itemPrintTitles="1" createdVersion="8" indent="0" outline="1" outlineData="1" multipleFieldFilters="0" chartFormat="14">
-  <location ref="I6:J9" firstHeaderRow="1" firstDataRow="1" firstDataCol="1"/>
-  <pivotFields count="13">
-    <pivotField showAll="0"/>
-    <pivotField showAll="0"/>
-    <pivotField showAll="0">
-      <items count="4">
-        <item x="1"/>
-        <item x="2"/>
-        <item x="0"/>
-        <item t="default"/>
-      </items>
-    </pivotField>
-    <pivotField numFmtId="14" showAll="0"/>
-    <pivotField axis="axisRow" showAll="0">
-      <items count="3">
-        <item x="1"/>
-        <item x="0"/>
-        <item t="default"/>
-      </items>
-    </pivotField>
-    <pivotField numFmtId="44" showAll="0"/>
-    <pivotField showAll="0"/>
-    <pivotField showAll="0"/>
-    <pivotField showAll="0"/>
-    <pivotField showAll="0"/>
-    <pivotField numFmtId="44" showAll="0"/>
-    <pivotField numFmtId="44" showAll="0"/>
-    <pivotField dataField="1" numFmtId="44" showAll="0"/>
-  </pivotFields>
-  <rowFields count="1">
-    <field x="4"/>
-  </rowFields>
-  <rowItems count="3">
-    <i>
-      <x/>
-    </i>
-    <i>
-      <x v="1"/>
-    </i>
-    <i t="grand">
-      <x/>
-    </i>
-  </rowItems>
-  <colItems count="1">
-    <i/>
-  </colItems>
-  <dataFields count="1">
-    <dataField name="Soma de Total Value" fld="12" baseField="0" baseItem="0" numFmtId="44"/>
-  </dataFields>
-  <chartFormats count="3">
-    <chartFormat chart="7" format="6" series="1">
-      <pivotArea type="data" outline="0" fieldPosition="0">
-        <references count="1">
-          <reference field="4294967294" count="1" selected="0">
-            <x v="0"/>
-          </reference>
-        </references>
-      </pivotArea>
-    </chartFormat>
-    <chartFormat chart="9" format="10" series="1">
-      <pivotArea type="data" outline="0" fieldPosition="0">
-        <references count="1">
-          <reference field="4294967294" count="1" selected="0">
-            <x v="0"/>
-          </reference>
-        </references>
-      </pivotArea>
-    </chartFormat>
-    <chartFormat chart="10" format="14" series="1">
-      <pivotArea type="data" outline="0" fieldPosition="0">
-        <references count="1">
-          <reference field="4294967294" count="1" selected="0">
-            <x v="0"/>
-          </reference>
-        </references>
-      </pivotArea>
-    </chartFormat>
-  </chartFormats>
-  <pivotTableStyleInfo name="PivotStyleLight16" showRowHeaders="1" showColHeaders="1" showRowStripes="0" showColStripes="0" showLastColumn="1"/>
-  <extLst>
-    <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{962EF5D1-5CA2-4c93-8EF4-DBF5C05439D2}">
-      <x14:pivotTableDefinition xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main" hideValuesRow="1"/>
-    </ext>
-    <ext xmlns:xpdl="http://schemas.microsoft.com/office/spreadsheetml/2016/pivotdefaultlayout" uri="{747A6164-185A-40DC-8AA5-F01512510D54}">
-      <xpdl:pivotTableDefinition16/>
-    </ext>
-  </extLst>
-</pivotTableDefinition>
-</file>
-
-<file path=xl/pivotTables/pivotTable2.xml><?xml version="1.0" encoding="utf-8"?>
-<pivotTableDefinition xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="xr" xr:uid="{0EEE0692-E80B-4E7A-920E-F3BB008BFEC9}" name="Tabela dinâmica2" cacheId="4" applyNumberFormats="0" applyBorderFormats="0" applyFontFormats="0" applyPatternFormats="0" applyAlignmentFormats="0" applyWidthHeightFormats="1" dataCaption="Valores" updatedVersion="8" minRefreshableVersion="3" useAutoFormatting="1" itemPrintTitles="1" createdVersion="8" indent="0" outline="1" outlineData="1" multipleFieldFilters="0" chartFormat="19">
-  <location ref="C14:F19" firstHeaderRow="1" firstDataRow="2" firstDataCol="1"/>
-  <pivotFields count="13">
-    <pivotField dataField="1" showAll="0"/>
-    <pivotField showAll="0"/>
-    <pivotField axis="axisRow" showAll="0">
-      <items count="4">
-        <item x="1"/>
-        <item x="2"/>
-        <item x="0"/>
-        <item t="default"/>
-      </items>
-    </pivotField>
-    <pivotField numFmtId="14" showAll="0"/>
-    <pivotField axis="axisCol" showAll="0">
-      <items count="3">
-        <item x="1"/>
-        <item x="0"/>
-        <item t="default"/>
-      </items>
-    </pivotField>
-    <pivotField numFmtId="44" showAll="0"/>
-    <pivotField showAll="0"/>
-    <pivotField showAll="0"/>
-    <pivotField showAll="0"/>
-    <pivotField showAll="0"/>
-    <pivotField numFmtId="44" showAll="0"/>
-    <pivotField numFmtId="44" showAll="0"/>
-    <pivotField numFmtId="44" showAll="0"/>
-  </pivotFields>
-  <rowFields count="1">
-    <field x="2"/>
-  </rowFields>
-  <rowItems count="4">
-    <i>
-      <x/>
-    </i>
-    <i>
-      <x v="1"/>
-    </i>
-    <i>
-      <x v="2"/>
-    </i>
-    <i t="grand">
-      <x/>
-    </i>
-  </rowItems>
-  <colFields count="1">
-    <field x="4"/>
-  </colFields>
-  <colItems count="3">
-    <i>
-      <x/>
-    </i>
-    <i>
-      <x v="1"/>
-    </i>
-    <i t="grand">
-      <x/>
-    </i>
-  </colItems>
-  <dataFields count="1">
-    <dataField name="Contagem de Subscriber ID" fld="0" subtotal="count" baseField="4" baseItem="0"/>
-  </dataFields>
-  <chartFormats count="4">
-    <chartFormat chart="13" format="8" series="1">
-      <pivotArea type="data" outline="0" fieldPosition="0">
-        <references count="2">
-          <reference field="4294967294" count="1" selected="0">
-            <x v="0"/>
-          </reference>
-          <reference field="4" count="1" selected="0">
-            <x v="0"/>
-          </reference>
-        </references>
-      </pivotArea>
-    </chartFormat>
-    <chartFormat chart="13" format="9" series="1">
-      <pivotArea type="data" outline="0" fieldPosition="0">
-        <references count="2">
-          <reference field="4294967294" count="1" selected="0">
-            <x v="0"/>
-          </reference>
-          <reference field="4" count="1" selected="0">
-            <x v="1"/>
-          </reference>
-        </references>
-      </pivotArea>
-    </chartFormat>
-    <chartFormat chart="17" format="12" series="1">
-      <pivotArea type="data" outline="0" fieldPosition="0">
-        <references count="2">
-          <reference field="4294967294" count="1" selected="0">
-            <x v="0"/>
-          </reference>
-          <reference field="4" count="1" selected="0">
-            <x v="0"/>
-          </reference>
-        </references>
-      </pivotArea>
-    </chartFormat>
-    <chartFormat chart="17" format="13" series="1">
-      <pivotArea type="data" outline="0" fieldPosition="0">
-        <references count="2">
-          <reference field="4294967294" count="1" selected="0">
-            <x v="0"/>
-          </reference>
-          <reference field="4" count="1" selected="0">
-            <x v="1"/>
-          </reference>
-        </references>
-      </pivotArea>
-    </chartFormat>
-  </chartFormats>
-  <pivotTableStyleInfo name="PivotStyleLight16" showRowHeaders="1" showColHeaders="1" showRowStripes="0" showColStripes="0" showLastColumn="1"/>
-  <extLst>
-    <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{962EF5D1-5CA2-4c93-8EF4-DBF5C05439D2}">
-      <x14:pivotTableDefinition xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main" hideValuesRow="1"/>
-    </ext>
-    <ext xmlns:xpdl="http://schemas.microsoft.com/office/spreadsheetml/2016/pivotdefaultlayout" uri="{747A6164-185A-40DC-8AA5-F01512510D54}">
-      <xpdl:pivotTableDefinition16/>
-    </ext>
-  </extLst>
-</pivotTableDefinition>
-</file>
-
-<file path=xl/pivotTables/pivotTable3.xml><?xml version="1.0" encoding="utf-8"?>
-<pivotTableDefinition xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="xr" xr:uid="{F20881AC-45B9-4186-9E89-A68CD89E33A5}" name="Tabela dinâmica1" cacheId="4" applyNumberFormats="0" applyBorderFormats="0" applyFontFormats="0" applyPatternFormats="0" applyAlignmentFormats="0" applyWidthHeightFormats="1" dataCaption="Valores" updatedVersion="8" minRefreshableVersion="3" useAutoFormatting="1" itemPrintTitles="1" createdVersion="8" indent="0" outline="1" outlineData="1" multipleFieldFilters="0" chartFormat="14">
+<pivotTableDefinition xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="xr" xr:uid="{F20881AC-45B9-4186-9E89-A68CD89E33A5}" name="Tabela dinâmica1" cacheId="0" applyNumberFormats="0" applyBorderFormats="0" applyFontFormats="0" applyPatternFormats="0" applyAlignmentFormats="0" applyWidthHeightFormats="1" dataCaption="Valores" updatedVersion="8" minRefreshableVersion="3" useAutoFormatting="1" itemPrintTitles="1" createdVersion="8" indent="0" outline="1" outlineData="1" multipleFieldFilters="0" chartFormat="14">
   <location ref="C6:D10" firstHeaderRow="1" firstDataRow="1" firstDataCol="1"/>
   <pivotFields count="13">
     <pivotField showAll="0"/>
@@ -10400,10 +11153,315 @@
         <item t="default"/>
       </items>
     </pivotField>
-    <pivotField numFmtId="14" showAll="0"/>
+    <pivotField numFmtId="14" showAll="0">
+      <items count="295">
+        <item x="0"/>
+        <item x="1"/>
+        <item x="2"/>
+        <item x="3"/>
+        <item x="5"/>
+        <item x="6"/>
+        <item x="7"/>
+        <item x="4"/>
+        <item x="8"/>
+        <item x="9"/>
+        <item x="10"/>
+        <item x="11"/>
+        <item x="12"/>
+        <item x="13"/>
+        <item x="14"/>
+        <item x="15"/>
+        <item x="16"/>
+        <item x="17"/>
+        <item x="18"/>
+        <item x="19"/>
+        <item x="20"/>
+        <item x="21"/>
+        <item x="22"/>
+        <item x="23"/>
+        <item x="24"/>
+        <item x="25"/>
+        <item x="26"/>
+        <item x="27"/>
+        <item x="28"/>
+        <item x="29"/>
+        <item x="30"/>
+        <item x="31"/>
+        <item x="32"/>
+        <item x="33"/>
+        <item x="34"/>
+        <item x="35"/>
+        <item x="36"/>
+        <item x="37"/>
+        <item x="38"/>
+        <item x="39"/>
+        <item x="40"/>
+        <item x="41"/>
+        <item x="42"/>
+        <item x="43"/>
+        <item x="44"/>
+        <item x="45"/>
+        <item x="46"/>
+        <item x="47"/>
+        <item x="48"/>
+        <item x="49"/>
+        <item x="50"/>
+        <item x="51"/>
+        <item x="52"/>
+        <item x="53"/>
+        <item x="54"/>
+        <item x="55"/>
+        <item x="56"/>
+        <item x="57"/>
+        <item x="58"/>
+        <item x="59"/>
+        <item x="60"/>
+        <item x="61"/>
+        <item x="62"/>
+        <item x="63"/>
+        <item x="64"/>
+        <item x="65"/>
+        <item x="66"/>
+        <item x="67"/>
+        <item x="68"/>
+        <item x="69"/>
+        <item x="70"/>
+        <item x="71"/>
+        <item x="72"/>
+        <item x="73"/>
+        <item x="74"/>
+        <item x="75"/>
+        <item x="76"/>
+        <item x="77"/>
+        <item x="78"/>
+        <item x="79"/>
+        <item x="80"/>
+        <item x="81"/>
+        <item x="82"/>
+        <item x="83"/>
+        <item x="84"/>
+        <item x="85"/>
+        <item x="86"/>
+        <item x="87"/>
+        <item x="88"/>
+        <item x="89"/>
+        <item x="90"/>
+        <item x="91"/>
+        <item x="92"/>
+        <item x="93"/>
+        <item x="94"/>
+        <item x="95"/>
+        <item x="96"/>
+        <item x="97"/>
+        <item x="98"/>
+        <item x="99"/>
+        <item x="100"/>
+        <item x="101"/>
+        <item x="102"/>
+        <item x="103"/>
+        <item x="104"/>
+        <item x="105"/>
+        <item x="106"/>
+        <item x="107"/>
+        <item x="108"/>
+        <item x="109"/>
+        <item x="110"/>
+        <item x="111"/>
+        <item x="112"/>
+        <item x="113"/>
+        <item x="114"/>
+        <item x="115"/>
+        <item x="116"/>
+        <item x="117"/>
+        <item x="118"/>
+        <item x="119"/>
+        <item x="120"/>
+        <item x="121"/>
+        <item x="122"/>
+        <item x="123"/>
+        <item x="124"/>
+        <item x="125"/>
+        <item x="126"/>
+        <item x="127"/>
+        <item x="128"/>
+        <item x="129"/>
+        <item x="130"/>
+        <item x="131"/>
+        <item x="132"/>
+        <item x="133"/>
+        <item x="134"/>
+        <item x="135"/>
+        <item x="136"/>
+        <item x="137"/>
+        <item x="138"/>
+        <item x="139"/>
+        <item x="140"/>
+        <item x="141"/>
+        <item x="142"/>
+        <item x="143"/>
+        <item x="144"/>
+        <item x="145"/>
+        <item x="146"/>
+        <item x="147"/>
+        <item x="148"/>
+        <item x="149"/>
+        <item x="150"/>
+        <item x="151"/>
+        <item x="152"/>
+        <item x="153"/>
+        <item x="154"/>
+        <item x="155"/>
+        <item x="156"/>
+        <item x="157"/>
+        <item x="158"/>
+        <item x="159"/>
+        <item x="160"/>
+        <item x="161"/>
+        <item x="162"/>
+        <item x="163"/>
+        <item x="164"/>
+        <item x="165"/>
+        <item x="166"/>
+        <item x="167"/>
+        <item x="168"/>
+        <item x="169"/>
+        <item x="170"/>
+        <item x="171"/>
+        <item x="172"/>
+        <item x="173"/>
+        <item x="174"/>
+        <item x="175"/>
+        <item x="176"/>
+        <item x="177"/>
+        <item x="178"/>
+        <item x="179"/>
+        <item x="180"/>
+        <item x="181"/>
+        <item x="182"/>
+        <item x="183"/>
+        <item x="184"/>
+        <item x="185"/>
+        <item x="186"/>
+        <item x="187"/>
+        <item x="188"/>
+        <item x="189"/>
+        <item x="190"/>
+        <item x="191"/>
+        <item x="192"/>
+        <item x="193"/>
+        <item x="194"/>
+        <item x="195"/>
+        <item x="196"/>
+        <item x="197"/>
+        <item x="198"/>
+        <item x="199"/>
+        <item x="200"/>
+        <item x="201"/>
+        <item x="202"/>
+        <item x="203"/>
+        <item x="204"/>
+        <item x="205"/>
+        <item x="206"/>
+        <item x="207"/>
+        <item x="208"/>
+        <item x="209"/>
+        <item x="210"/>
+        <item x="211"/>
+        <item x="212"/>
+        <item x="213"/>
+        <item x="214"/>
+        <item x="215"/>
+        <item x="216"/>
+        <item x="217"/>
+        <item x="218"/>
+        <item x="219"/>
+        <item x="220"/>
+        <item x="221"/>
+        <item x="222"/>
+        <item x="223"/>
+        <item x="224"/>
+        <item x="225"/>
+        <item x="226"/>
+        <item x="227"/>
+        <item x="228"/>
+        <item x="229"/>
+        <item x="230"/>
+        <item x="231"/>
+        <item x="232"/>
+        <item x="233"/>
+        <item x="234"/>
+        <item x="235"/>
+        <item x="236"/>
+        <item x="237"/>
+        <item x="238"/>
+        <item x="239"/>
+        <item x="240"/>
+        <item x="241"/>
+        <item x="242"/>
+        <item x="243"/>
+        <item x="244"/>
+        <item x="245"/>
+        <item x="246"/>
+        <item x="247"/>
+        <item x="248"/>
+        <item x="249"/>
+        <item x="250"/>
+        <item x="251"/>
+        <item x="252"/>
+        <item x="253"/>
+        <item x="254"/>
+        <item x="255"/>
+        <item x="256"/>
+        <item x="257"/>
+        <item x="258"/>
+        <item x="259"/>
+        <item x="260"/>
+        <item x="261"/>
+        <item x="262"/>
+        <item x="263"/>
+        <item x="264"/>
+        <item x="265"/>
+        <item x="266"/>
+        <item x="267"/>
+        <item x="268"/>
+        <item x="269"/>
+        <item x="270"/>
+        <item x="271"/>
+        <item x="272"/>
+        <item x="273"/>
+        <item x="274"/>
+        <item x="275"/>
+        <item x="276"/>
+        <item x="277"/>
+        <item x="278"/>
+        <item x="279"/>
+        <item x="280"/>
+        <item x="281"/>
+        <item x="282"/>
+        <item x="283"/>
+        <item x="284"/>
+        <item x="285"/>
+        <item x="286"/>
+        <item x="287"/>
+        <item x="288"/>
+        <item x="289"/>
+        <item x="290"/>
+        <item x="291"/>
+        <item x="292"/>
+        <item x="293"/>
+        <item t="default"/>
+      </items>
+    </pivotField>
     <pivotField showAll="0"/>
     <pivotField numFmtId="44" showAll="0"/>
-    <pivotField showAll="0"/>
+    <pivotField showAll="0">
+      <items count="4">
+        <item h="1" x="1"/>
+        <item x="0"/>
+        <item h="1" x="2"/>
+        <item t="default"/>
+      </items>
+    </pivotField>
     <pivotField showAll="0"/>
     <pivotField showAll="0"/>
     <pivotField showAll="0"/>
@@ -10581,6 +11639,860 @@
     </ext>
   </extLst>
 </pivotTableDefinition>
+</file>
+
+<file path=xl/pivotTables/pivotTable2.xml><?xml version="1.0" encoding="utf-8"?>
+<pivotTableDefinition xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="xr" xr:uid="{36A8AA56-C674-410D-B731-334A08BD7462}" name="Tabela dinâmica3" cacheId="0" applyNumberFormats="0" applyBorderFormats="0" applyFontFormats="0" applyPatternFormats="0" applyAlignmentFormats="0" applyWidthHeightFormats="1" dataCaption="Valores" updatedVersion="8" minRefreshableVersion="3" useAutoFormatting="1" itemPrintTitles="1" createdVersion="8" indent="0" outline="1" outlineData="1" multipleFieldFilters="0" chartFormat="14">
+  <location ref="I6:J9" firstHeaderRow="1" firstDataRow="1" firstDataCol="1"/>
+  <pivotFields count="13">
+    <pivotField showAll="0"/>
+    <pivotField showAll="0"/>
+    <pivotField showAll="0">
+      <items count="4">
+        <item x="1"/>
+        <item x="2"/>
+        <item x="0"/>
+        <item t="default"/>
+      </items>
+    </pivotField>
+    <pivotField numFmtId="14" showAll="0">
+      <items count="295">
+        <item x="0"/>
+        <item x="1"/>
+        <item x="2"/>
+        <item x="3"/>
+        <item x="5"/>
+        <item x="6"/>
+        <item x="7"/>
+        <item x="4"/>
+        <item x="8"/>
+        <item x="9"/>
+        <item x="10"/>
+        <item x="11"/>
+        <item x="12"/>
+        <item x="13"/>
+        <item x="14"/>
+        <item x="15"/>
+        <item x="16"/>
+        <item x="17"/>
+        <item x="18"/>
+        <item x="19"/>
+        <item x="20"/>
+        <item x="21"/>
+        <item x="22"/>
+        <item x="23"/>
+        <item x="24"/>
+        <item x="25"/>
+        <item x="26"/>
+        <item x="27"/>
+        <item x="28"/>
+        <item x="29"/>
+        <item x="30"/>
+        <item x="31"/>
+        <item x="32"/>
+        <item x="33"/>
+        <item x="34"/>
+        <item x="35"/>
+        <item x="36"/>
+        <item x="37"/>
+        <item x="38"/>
+        <item x="39"/>
+        <item x="40"/>
+        <item x="41"/>
+        <item x="42"/>
+        <item x="43"/>
+        <item x="44"/>
+        <item x="45"/>
+        <item x="46"/>
+        <item x="47"/>
+        <item x="48"/>
+        <item x="49"/>
+        <item x="50"/>
+        <item x="51"/>
+        <item x="52"/>
+        <item x="53"/>
+        <item x="54"/>
+        <item x="55"/>
+        <item x="56"/>
+        <item x="57"/>
+        <item x="58"/>
+        <item x="59"/>
+        <item x="60"/>
+        <item x="61"/>
+        <item x="62"/>
+        <item x="63"/>
+        <item x="64"/>
+        <item x="65"/>
+        <item x="66"/>
+        <item x="67"/>
+        <item x="68"/>
+        <item x="69"/>
+        <item x="70"/>
+        <item x="71"/>
+        <item x="72"/>
+        <item x="73"/>
+        <item x="74"/>
+        <item x="75"/>
+        <item x="76"/>
+        <item x="77"/>
+        <item x="78"/>
+        <item x="79"/>
+        <item x="80"/>
+        <item x="81"/>
+        <item x="82"/>
+        <item x="83"/>
+        <item x="84"/>
+        <item x="85"/>
+        <item x="86"/>
+        <item x="87"/>
+        <item x="88"/>
+        <item x="89"/>
+        <item x="90"/>
+        <item x="91"/>
+        <item x="92"/>
+        <item x="93"/>
+        <item x="94"/>
+        <item x="95"/>
+        <item x="96"/>
+        <item x="97"/>
+        <item x="98"/>
+        <item x="99"/>
+        <item x="100"/>
+        <item x="101"/>
+        <item x="102"/>
+        <item x="103"/>
+        <item x="104"/>
+        <item x="105"/>
+        <item x="106"/>
+        <item x="107"/>
+        <item x="108"/>
+        <item x="109"/>
+        <item x="110"/>
+        <item x="111"/>
+        <item x="112"/>
+        <item x="113"/>
+        <item x="114"/>
+        <item x="115"/>
+        <item x="116"/>
+        <item x="117"/>
+        <item x="118"/>
+        <item x="119"/>
+        <item x="120"/>
+        <item x="121"/>
+        <item x="122"/>
+        <item x="123"/>
+        <item x="124"/>
+        <item x="125"/>
+        <item x="126"/>
+        <item x="127"/>
+        <item x="128"/>
+        <item x="129"/>
+        <item x="130"/>
+        <item x="131"/>
+        <item x="132"/>
+        <item x="133"/>
+        <item x="134"/>
+        <item x="135"/>
+        <item x="136"/>
+        <item x="137"/>
+        <item x="138"/>
+        <item x="139"/>
+        <item x="140"/>
+        <item x="141"/>
+        <item x="142"/>
+        <item x="143"/>
+        <item x="144"/>
+        <item x="145"/>
+        <item x="146"/>
+        <item x="147"/>
+        <item x="148"/>
+        <item x="149"/>
+        <item x="150"/>
+        <item x="151"/>
+        <item x="152"/>
+        <item x="153"/>
+        <item x="154"/>
+        <item x="155"/>
+        <item x="156"/>
+        <item x="157"/>
+        <item x="158"/>
+        <item x="159"/>
+        <item x="160"/>
+        <item x="161"/>
+        <item x="162"/>
+        <item x="163"/>
+        <item x="164"/>
+        <item x="165"/>
+        <item x="166"/>
+        <item x="167"/>
+        <item x="168"/>
+        <item x="169"/>
+        <item x="170"/>
+        <item x="171"/>
+        <item x="172"/>
+        <item x="173"/>
+        <item x="174"/>
+        <item x="175"/>
+        <item x="176"/>
+        <item x="177"/>
+        <item x="178"/>
+        <item x="179"/>
+        <item x="180"/>
+        <item x="181"/>
+        <item x="182"/>
+        <item x="183"/>
+        <item x="184"/>
+        <item x="185"/>
+        <item x="186"/>
+        <item x="187"/>
+        <item x="188"/>
+        <item x="189"/>
+        <item x="190"/>
+        <item x="191"/>
+        <item x="192"/>
+        <item x="193"/>
+        <item x="194"/>
+        <item x="195"/>
+        <item x="196"/>
+        <item x="197"/>
+        <item x="198"/>
+        <item x="199"/>
+        <item x="200"/>
+        <item x="201"/>
+        <item x="202"/>
+        <item x="203"/>
+        <item x="204"/>
+        <item x="205"/>
+        <item x="206"/>
+        <item x="207"/>
+        <item x="208"/>
+        <item x="209"/>
+        <item x="210"/>
+        <item x="211"/>
+        <item x="212"/>
+        <item x="213"/>
+        <item x="214"/>
+        <item x="215"/>
+        <item x="216"/>
+        <item x="217"/>
+        <item x="218"/>
+        <item x="219"/>
+        <item x="220"/>
+        <item x="221"/>
+        <item x="222"/>
+        <item x="223"/>
+        <item x="224"/>
+        <item x="225"/>
+        <item x="226"/>
+        <item x="227"/>
+        <item x="228"/>
+        <item x="229"/>
+        <item x="230"/>
+        <item x="231"/>
+        <item x="232"/>
+        <item x="233"/>
+        <item x="234"/>
+        <item x="235"/>
+        <item x="236"/>
+        <item x="237"/>
+        <item x="238"/>
+        <item x="239"/>
+        <item x="240"/>
+        <item x="241"/>
+        <item x="242"/>
+        <item x="243"/>
+        <item x="244"/>
+        <item x="245"/>
+        <item x="246"/>
+        <item x="247"/>
+        <item x="248"/>
+        <item x="249"/>
+        <item x="250"/>
+        <item x="251"/>
+        <item x="252"/>
+        <item x="253"/>
+        <item x="254"/>
+        <item x="255"/>
+        <item x="256"/>
+        <item x="257"/>
+        <item x="258"/>
+        <item x="259"/>
+        <item x="260"/>
+        <item x="261"/>
+        <item x="262"/>
+        <item x="263"/>
+        <item x="264"/>
+        <item x="265"/>
+        <item x="266"/>
+        <item x="267"/>
+        <item x="268"/>
+        <item x="269"/>
+        <item x="270"/>
+        <item x="271"/>
+        <item x="272"/>
+        <item x="273"/>
+        <item x="274"/>
+        <item x="275"/>
+        <item x="276"/>
+        <item x="277"/>
+        <item x="278"/>
+        <item x="279"/>
+        <item x="280"/>
+        <item x="281"/>
+        <item x="282"/>
+        <item x="283"/>
+        <item x="284"/>
+        <item x="285"/>
+        <item x="286"/>
+        <item x="287"/>
+        <item x="288"/>
+        <item x="289"/>
+        <item x="290"/>
+        <item x="291"/>
+        <item x="292"/>
+        <item x="293"/>
+        <item t="default"/>
+      </items>
+    </pivotField>
+    <pivotField axis="axisRow" showAll="0">
+      <items count="3">
+        <item x="1"/>
+        <item x="0"/>
+        <item t="default"/>
+      </items>
+    </pivotField>
+    <pivotField numFmtId="44" showAll="0"/>
+    <pivotField showAll="0">
+      <items count="4">
+        <item h="1" x="1"/>
+        <item x="0"/>
+        <item h="1" x="2"/>
+        <item t="default"/>
+      </items>
+    </pivotField>
+    <pivotField showAll="0"/>
+    <pivotField showAll="0"/>
+    <pivotField showAll="0"/>
+    <pivotField numFmtId="44" showAll="0"/>
+    <pivotField numFmtId="44" showAll="0"/>
+    <pivotField dataField="1" numFmtId="44" showAll="0"/>
+  </pivotFields>
+  <rowFields count="1">
+    <field x="4"/>
+  </rowFields>
+  <rowItems count="3">
+    <i>
+      <x/>
+    </i>
+    <i>
+      <x v="1"/>
+    </i>
+    <i t="grand">
+      <x/>
+    </i>
+  </rowItems>
+  <colItems count="1">
+    <i/>
+  </colItems>
+  <dataFields count="1">
+    <dataField name="Soma de Total Value" fld="12" baseField="0" baseItem="0" numFmtId="44"/>
+  </dataFields>
+  <chartFormats count="3">
+    <chartFormat chart="7" format="6" series="1">
+      <pivotArea type="data" outline="0" fieldPosition="0">
+        <references count="1">
+          <reference field="4294967294" count="1" selected="0">
+            <x v="0"/>
+          </reference>
+        </references>
+      </pivotArea>
+    </chartFormat>
+    <chartFormat chart="9" format="10" series="1">
+      <pivotArea type="data" outline="0" fieldPosition="0">
+        <references count="1">
+          <reference field="4294967294" count="1" selected="0">
+            <x v="0"/>
+          </reference>
+        </references>
+      </pivotArea>
+    </chartFormat>
+    <chartFormat chart="10" format="14" series="1">
+      <pivotArea type="data" outline="0" fieldPosition="0">
+        <references count="1">
+          <reference field="4294967294" count="1" selected="0">
+            <x v="0"/>
+          </reference>
+        </references>
+      </pivotArea>
+    </chartFormat>
+  </chartFormats>
+  <pivotTableStyleInfo name="PivotStyleLight16" showRowHeaders="1" showColHeaders="1" showRowStripes="0" showColStripes="0" showLastColumn="1"/>
+  <extLst>
+    <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{962EF5D1-5CA2-4c93-8EF4-DBF5C05439D2}">
+      <x14:pivotTableDefinition xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main" hideValuesRow="1"/>
+    </ext>
+    <ext xmlns:xpdl="http://schemas.microsoft.com/office/spreadsheetml/2016/pivotdefaultlayout" uri="{747A6164-185A-40DC-8AA5-F01512510D54}">
+      <xpdl:pivotTableDefinition16/>
+    </ext>
+  </extLst>
+</pivotTableDefinition>
+</file>
+
+<file path=xl/pivotTables/pivotTable3.xml><?xml version="1.0" encoding="utf-8"?>
+<pivotTableDefinition xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="xr" xr:uid="{0EEE0692-E80B-4E7A-920E-F3BB008BFEC9}" name="Tabela dinâmica2" cacheId="0" applyNumberFormats="0" applyBorderFormats="0" applyFontFormats="0" applyPatternFormats="0" applyAlignmentFormats="0" applyWidthHeightFormats="1" dataCaption="Valores" updatedVersion="8" minRefreshableVersion="3" useAutoFormatting="1" itemPrintTitles="1" createdVersion="8" indent="0" outline="1" outlineData="1" multipleFieldFilters="0" chartFormat="19">
+  <location ref="C14:F19" firstHeaderRow="1" firstDataRow="2" firstDataCol="1"/>
+  <pivotFields count="13">
+    <pivotField dataField="1" showAll="0"/>
+    <pivotField showAll="0"/>
+    <pivotField axis="axisRow" showAll="0">
+      <items count="4">
+        <item x="1"/>
+        <item x="2"/>
+        <item x="0"/>
+        <item t="default"/>
+      </items>
+    </pivotField>
+    <pivotField numFmtId="14" showAll="0">
+      <items count="295">
+        <item x="0"/>
+        <item x="1"/>
+        <item x="2"/>
+        <item x="3"/>
+        <item x="5"/>
+        <item x="6"/>
+        <item x="7"/>
+        <item x="4"/>
+        <item x="8"/>
+        <item x="9"/>
+        <item x="10"/>
+        <item x="11"/>
+        <item x="12"/>
+        <item x="13"/>
+        <item x="14"/>
+        <item x="15"/>
+        <item x="16"/>
+        <item x="17"/>
+        <item x="18"/>
+        <item x="19"/>
+        <item x="20"/>
+        <item x="21"/>
+        <item x="22"/>
+        <item x="23"/>
+        <item x="24"/>
+        <item x="25"/>
+        <item x="26"/>
+        <item x="27"/>
+        <item x="28"/>
+        <item x="29"/>
+        <item x="30"/>
+        <item x="31"/>
+        <item x="32"/>
+        <item x="33"/>
+        <item x="34"/>
+        <item x="35"/>
+        <item x="36"/>
+        <item x="37"/>
+        <item x="38"/>
+        <item x="39"/>
+        <item x="40"/>
+        <item x="41"/>
+        <item x="42"/>
+        <item x="43"/>
+        <item x="44"/>
+        <item x="45"/>
+        <item x="46"/>
+        <item x="47"/>
+        <item x="48"/>
+        <item x="49"/>
+        <item x="50"/>
+        <item x="51"/>
+        <item x="52"/>
+        <item x="53"/>
+        <item x="54"/>
+        <item x="55"/>
+        <item x="56"/>
+        <item x="57"/>
+        <item x="58"/>
+        <item x="59"/>
+        <item x="60"/>
+        <item x="61"/>
+        <item x="62"/>
+        <item x="63"/>
+        <item x="64"/>
+        <item x="65"/>
+        <item x="66"/>
+        <item x="67"/>
+        <item x="68"/>
+        <item x="69"/>
+        <item x="70"/>
+        <item x="71"/>
+        <item x="72"/>
+        <item x="73"/>
+        <item x="74"/>
+        <item x="75"/>
+        <item x="76"/>
+        <item x="77"/>
+        <item x="78"/>
+        <item x="79"/>
+        <item x="80"/>
+        <item x="81"/>
+        <item x="82"/>
+        <item x="83"/>
+        <item x="84"/>
+        <item x="85"/>
+        <item x="86"/>
+        <item x="87"/>
+        <item x="88"/>
+        <item x="89"/>
+        <item x="90"/>
+        <item x="91"/>
+        <item x="92"/>
+        <item x="93"/>
+        <item x="94"/>
+        <item x="95"/>
+        <item x="96"/>
+        <item x="97"/>
+        <item x="98"/>
+        <item x="99"/>
+        <item x="100"/>
+        <item x="101"/>
+        <item x="102"/>
+        <item x="103"/>
+        <item x="104"/>
+        <item x="105"/>
+        <item x="106"/>
+        <item x="107"/>
+        <item x="108"/>
+        <item x="109"/>
+        <item x="110"/>
+        <item x="111"/>
+        <item x="112"/>
+        <item x="113"/>
+        <item x="114"/>
+        <item x="115"/>
+        <item x="116"/>
+        <item x="117"/>
+        <item x="118"/>
+        <item x="119"/>
+        <item x="120"/>
+        <item x="121"/>
+        <item x="122"/>
+        <item x="123"/>
+        <item x="124"/>
+        <item x="125"/>
+        <item x="126"/>
+        <item x="127"/>
+        <item x="128"/>
+        <item x="129"/>
+        <item x="130"/>
+        <item x="131"/>
+        <item x="132"/>
+        <item x="133"/>
+        <item x="134"/>
+        <item x="135"/>
+        <item x="136"/>
+        <item x="137"/>
+        <item x="138"/>
+        <item x="139"/>
+        <item x="140"/>
+        <item x="141"/>
+        <item x="142"/>
+        <item x="143"/>
+        <item x="144"/>
+        <item x="145"/>
+        <item x="146"/>
+        <item x="147"/>
+        <item x="148"/>
+        <item x="149"/>
+        <item x="150"/>
+        <item x="151"/>
+        <item x="152"/>
+        <item x="153"/>
+        <item x="154"/>
+        <item x="155"/>
+        <item x="156"/>
+        <item x="157"/>
+        <item x="158"/>
+        <item x="159"/>
+        <item x="160"/>
+        <item x="161"/>
+        <item x="162"/>
+        <item x="163"/>
+        <item x="164"/>
+        <item x="165"/>
+        <item x="166"/>
+        <item x="167"/>
+        <item x="168"/>
+        <item x="169"/>
+        <item x="170"/>
+        <item x="171"/>
+        <item x="172"/>
+        <item x="173"/>
+        <item x="174"/>
+        <item x="175"/>
+        <item x="176"/>
+        <item x="177"/>
+        <item x="178"/>
+        <item x="179"/>
+        <item x="180"/>
+        <item x="181"/>
+        <item x="182"/>
+        <item x="183"/>
+        <item x="184"/>
+        <item x="185"/>
+        <item x="186"/>
+        <item x="187"/>
+        <item x="188"/>
+        <item x="189"/>
+        <item x="190"/>
+        <item x="191"/>
+        <item x="192"/>
+        <item x="193"/>
+        <item x="194"/>
+        <item x="195"/>
+        <item x="196"/>
+        <item x="197"/>
+        <item x="198"/>
+        <item x="199"/>
+        <item x="200"/>
+        <item x="201"/>
+        <item x="202"/>
+        <item x="203"/>
+        <item x="204"/>
+        <item x="205"/>
+        <item x="206"/>
+        <item x="207"/>
+        <item x="208"/>
+        <item x="209"/>
+        <item x="210"/>
+        <item x="211"/>
+        <item x="212"/>
+        <item x="213"/>
+        <item x="214"/>
+        <item x="215"/>
+        <item x="216"/>
+        <item x="217"/>
+        <item x="218"/>
+        <item x="219"/>
+        <item x="220"/>
+        <item x="221"/>
+        <item x="222"/>
+        <item x="223"/>
+        <item x="224"/>
+        <item x="225"/>
+        <item x="226"/>
+        <item x="227"/>
+        <item x="228"/>
+        <item x="229"/>
+        <item x="230"/>
+        <item x="231"/>
+        <item x="232"/>
+        <item x="233"/>
+        <item x="234"/>
+        <item x="235"/>
+        <item x="236"/>
+        <item x="237"/>
+        <item x="238"/>
+        <item x="239"/>
+        <item x="240"/>
+        <item x="241"/>
+        <item x="242"/>
+        <item x="243"/>
+        <item x="244"/>
+        <item x="245"/>
+        <item x="246"/>
+        <item x="247"/>
+        <item x="248"/>
+        <item x="249"/>
+        <item x="250"/>
+        <item x="251"/>
+        <item x="252"/>
+        <item x="253"/>
+        <item x="254"/>
+        <item x="255"/>
+        <item x="256"/>
+        <item x="257"/>
+        <item x="258"/>
+        <item x="259"/>
+        <item x="260"/>
+        <item x="261"/>
+        <item x="262"/>
+        <item x="263"/>
+        <item x="264"/>
+        <item x="265"/>
+        <item x="266"/>
+        <item x="267"/>
+        <item x="268"/>
+        <item x="269"/>
+        <item x="270"/>
+        <item x="271"/>
+        <item x="272"/>
+        <item x="273"/>
+        <item x="274"/>
+        <item x="275"/>
+        <item x="276"/>
+        <item x="277"/>
+        <item x="278"/>
+        <item x="279"/>
+        <item x="280"/>
+        <item x="281"/>
+        <item x="282"/>
+        <item x="283"/>
+        <item x="284"/>
+        <item x="285"/>
+        <item x="286"/>
+        <item x="287"/>
+        <item x="288"/>
+        <item x="289"/>
+        <item x="290"/>
+        <item x="291"/>
+        <item x="292"/>
+        <item x="293"/>
+        <item t="default"/>
+      </items>
+    </pivotField>
+    <pivotField axis="axisCol" showAll="0">
+      <items count="3">
+        <item x="1"/>
+        <item x="0"/>
+        <item t="default"/>
+      </items>
+    </pivotField>
+    <pivotField numFmtId="44" showAll="0"/>
+    <pivotField showAll="0">
+      <items count="4">
+        <item h="1" x="1"/>
+        <item x="0"/>
+        <item h="1" x="2"/>
+        <item t="default"/>
+      </items>
+    </pivotField>
+    <pivotField showAll="0"/>
+    <pivotField showAll="0"/>
+    <pivotField showAll="0"/>
+    <pivotField numFmtId="44" showAll="0"/>
+    <pivotField numFmtId="44" showAll="0"/>
+    <pivotField numFmtId="44" showAll="0"/>
+  </pivotFields>
+  <rowFields count="1">
+    <field x="2"/>
+  </rowFields>
+  <rowItems count="4">
+    <i>
+      <x/>
+    </i>
+    <i>
+      <x v="1"/>
+    </i>
+    <i>
+      <x v="2"/>
+    </i>
+    <i t="grand">
+      <x/>
+    </i>
+  </rowItems>
+  <colFields count="1">
+    <field x="4"/>
+  </colFields>
+  <colItems count="3">
+    <i>
+      <x/>
+    </i>
+    <i>
+      <x v="1"/>
+    </i>
+    <i t="grand">
+      <x/>
+    </i>
+  </colItems>
+  <dataFields count="1">
+    <dataField name="Contagem de Subscriber ID" fld="0" subtotal="count" baseField="4" baseItem="0"/>
+  </dataFields>
+  <chartFormats count="4">
+    <chartFormat chart="13" format="8" series="1">
+      <pivotArea type="data" outline="0" fieldPosition="0">
+        <references count="2">
+          <reference field="4294967294" count="1" selected="0">
+            <x v="0"/>
+          </reference>
+          <reference field="4" count="1" selected="0">
+            <x v="0"/>
+          </reference>
+        </references>
+      </pivotArea>
+    </chartFormat>
+    <chartFormat chart="13" format="9" series="1">
+      <pivotArea type="data" outline="0" fieldPosition="0">
+        <references count="2">
+          <reference field="4294967294" count="1" selected="0">
+            <x v="0"/>
+          </reference>
+          <reference field="4" count="1" selected="0">
+            <x v="1"/>
+          </reference>
+        </references>
+      </pivotArea>
+    </chartFormat>
+    <chartFormat chart="17" format="12" series="1">
+      <pivotArea type="data" outline="0" fieldPosition="0">
+        <references count="2">
+          <reference field="4294967294" count="1" selected="0">
+            <x v="0"/>
+          </reference>
+          <reference field="4" count="1" selected="0">
+            <x v="0"/>
+          </reference>
+        </references>
+      </pivotArea>
+    </chartFormat>
+    <chartFormat chart="17" format="13" series="1">
+      <pivotArea type="data" outline="0" fieldPosition="0">
+        <references count="2">
+          <reference field="4294967294" count="1" selected="0">
+            <x v="0"/>
+          </reference>
+          <reference field="4" count="1" selected="0">
+            <x v="1"/>
+          </reference>
+        </references>
+      </pivotArea>
+    </chartFormat>
+  </chartFormats>
+  <pivotTableStyleInfo name="PivotStyleLight16" showRowHeaders="1" showColHeaders="1" showRowStripes="0" showColStripes="0" showLastColumn="1"/>
+  <extLst>
+    <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{962EF5D1-5CA2-4c93-8EF4-DBF5C05439D2}">
+      <x14:pivotTableDefinition xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main" hideValuesRow="1"/>
+    </ext>
+    <ext xmlns:xpdl="http://schemas.microsoft.com/office/spreadsheetml/2016/pivotdefaultlayout" uri="{747A6164-185A-40DC-8AA5-F01512510D54}">
+      <xpdl:pivotTableDefinition16/>
+    </ext>
+  </extLst>
+</pivotTableDefinition>
+</file>
+
+<file path=xl/slicerCaches/slicerCache1.xml><?xml version="1.0" encoding="utf-8"?>
+<slicerCacheDefinition xmlns="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" mc:Ignorable="x xr10" name="SegmentaçãodeDados_Subscription_Type" xr10:uid="{FAC0F0AF-CB8F-4C88-9E68-BF7D5C93A6D9}" sourceName="Subscription Type">
+  <pivotTables>
+    <pivotTable tabId="3" name="Tabela dinâmica2"/>
+    <pivotTable tabId="3" name="Tabela dinâmica1"/>
+    <pivotTable tabId="3" name="Tabela dinâmica3"/>
+  </pivotTables>
+  <data>
+    <tabular pivotCacheId="1683066976" crossFilter="showItemsWithNoData">
+      <items count="3">
+        <i x="1"/>
+        <i x="0" s="1"/>
+        <i x="2"/>
+      </items>
+    </tabular>
+  </data>
+</slicerCacheDefinition>
+</file>
+
+<file path=xl/slicers/slicer1.xml><?xml version="1.0" encoding="utf-8"?>
+<slicers xmlns="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" mc:Ignorable="x xr10">
+  <slicer name="Subscription Type" xr10:uid="{D746B21C-59FA-4246-AB08-CCADD924B4F4}" cache="SegmentaçãodeDados_Subscription_Type" caption="SUBSCRIPTION TYPE" rowHeight="247650"/>
+</slicers>
 </file>
 
 <file path=xl/tables/table1.xml><?xml version="1.0" encoding="utf-8"?>
@@ -23270,9 +25182,9 @@
   <dimension ref="C6:J19"/>
   <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
-    <col min="3" max="3" width="23.77734375" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="18.109375" bestFit="1" customWidth="1"/>
-    <col min="5" max="5" width="4" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="16.77734375" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="17.88671875" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="3.88671875" bestFit="1" customWidth="1"/>
     <col min="6" max="7" width="10" bestFit="1" customWidth="1"/>
     <col min="8" max="8" width="11.88671875" bestFit="1" customWidth="1"/>
     <col min="9" max="9" width="16.77734375" bestFit="1" customWidth="1"/>
@@ -23302,13 +25214,13 @@
         <v>22</v>
       </c>
       <c r="D7" s="12">
-        <v>444</v>
+        <v>192</v>
       </c>
       <c r="I7" s="14" t="s">
         <v>23</v>
       </c>
       <c r="J7" s="12">
-        <v>3847</v>
+        <v>2824</v>
       </c>
     </row>
     <row r="8" spans="3:10" x14ac:dyDescent="0.3">
@@ -23316,17 +25228,17 @@
         <v>26</v>
       </c>
       <c r="D8" s="12">
-        <v>1801</v>
+        <v>958</v>
       </c>
       <c r="H8" s="15">
         <f>GETPIVOTDATA("Total Value",$C$6)</f>
-        <v>7633</v>
+        <v>3571</v>
       </c>
       <c r="I8" s="14" t="s">
         <v>19</v>
       </c>
       <c r="J8" s="12">
-        <v>3786</v>
+        <v>747</v>
       </c>
     </row>
     <row r="9" spans="3:10" x14ac:dyDescent="0.3">
@@ -23334,17 +25246,17 @@
         <v>18</v>
       </c>
       <c r="D9" s="12">
-        <v>5388</v>
+        <v>2421</v>
       </c>
       <c r="H9" s="15">
         <f>GETPIVOTDATA("Total Value",$I$6,"Auto Renewal","Yes")</f>
-        <v>3786</v>
+        <v>747</v>
       </c>
       <c r="I9" s="14" t="s">
         <v>315</v>
       </c>
       <c r="J9" s="12">
-        <v>7633</v>
+        <v>3571</v>
       </c>
     </row>
     <row r="10" spans="3:10" x14ac:dyDescent="0.3">
@@ -23352,7 +25264,7 @@
         <v>315</v>
       </c>
       <c r="D10" s="12">
-        <v>7633</v>
+        <v>3571</v>
       </c>
       <c r="G10" s="15"/>
     </row>
@@ -23382,56 +25294,56 @@
       <c r="C16" s="14" t="s">
         <v>22</v>
       </c>
-      <c r="D16" s="18">
-        <v>50</v>
-      </c>
-      <c r="E16" s="18">
-        <v>51</v>
-      </c>
-      <c r="F16" s="18">
-        <v>101</v>
+      <c r="D16">
+        <v>37</v>
+      </c>
+      <c r="E16">
+        <v>12</v>
+      </c>
+      <c r="F16">
+        <v>49</v>
       </c>
     </row>
     <row r="17" spans="3:6" x14ac:dyDescent="0.3">
       <c r="C17" s="14" t="s">
         <v>26</v>
       </c>
-      <c r="D17" s="18">
-        <v>47</v>
-      </c>
-      <c r="E17" s="18">
-        <v>49</v>
-      </c>
-      <c r="F17" s="18">
-        <v>96</v>
+      <c r="D17">
+        <v>40</v>
+      </c>
+      <c r="E17">
+        <v>5</v>
+      </c>
+      <c r="F17">
+        <v>45</v>
       </c>
     </row>
     <row r="18" spans="3:6" x14ac:dyDescent="0.3">
       <c r="C18" s="14" t="s">
         <v>18</v>
       </c>
-      <c r="D18" s="18">
-        <v>50</v>
-      </c>
-      <c r="E18" s="18">
-        <v>48</v>
-      </c>
-      <c r="F18" s="18">
-        <v>98</v>
+      <c r="D18">
+        <v>34</v>
+      </c>
+      <c r="E18">
+        <v>11</v>
+      </c>
+      <c r="F18">
+        <v>45</v>
       </c>
     </row>
     <row r="19" spans="3:6" x14ac:dyDescent="0.3">
       <c r="C19" s="14" t="s">
         <v>315</v>
       </c>
-      <c r="D19" s="18">
-        <v>147</v>
-      </c>
-      <c r="E19" s="18">
-        <v>148</v>
-      </c>
-      <c r="F19" s="18">
-        <v>295</v>
+      <c r="D19">
+        <v>111</v>
+      </c>
+      <c r="E19">
+        <v>28</v>
+      </c>
+      <c r="F19">
+        <v>139</v>
       </c>
     </row>
   </sheetData>
@@ -23445,7 +25357,7 @@
   <dimension ref="A1:C7"/>
   <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
-    <col min="1" max="1" width="20" style="5" customWidth="1"/>
+    <col min="1" max="1" width="29.44140625" style="5" customWidth="1"/>
     <col min="2" max="2" width="3.5546875" style="17" customWidth="1"/>
     <col min="3" max="11" width="8.88671875" style="17"/>
     <col min="12" max="12" width="6.5546875" style="17" customWidth="1"/>
@@ -23467,30 +25379,17 @@
   </sheetData>
   <pageMargins left="0.511811024" right="0.511811024" top="0.78740157499999996" bottom="0.78740157499999996" header="0.31496062000000002" footer="0.31496062000000002"/>
   <drawing r:id="rId1"/>
+  <extLst>
+    <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{A8765BA9-456A-4dab-B4F3-ACF838C121DE}">
+      <x14:slicerList>
+        <x14:slicer r:id="rId2"/>
+      </x14:slicerList>
+    </ext>
+  </extLst>
 </worksheet>
 </file>
 
 <file path=customXml/item1.xml><?xml version="1.0" encoding="utf-8"?>
-<p:properties xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls">
-  <documentManagement>
-    <lcf76f155ced4ddcb4097134ff3c332f xmlns="851b35d3-0456-4d6a-bc2f-da927e91d158">
-      <Terms xmlns="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
-    </lcf76f155ced4ddcb4097134ff3c332f>
-    <TaxCatchAll xmlns="19483571-f922-4e8e-9c1c-26f0a2252132" xsi:nil="true"/>
-  </documentManagement>
-</p:properties>
-</file>
-
-<file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
-<?mso-contentType ?>
-<FormTemplates xmlns="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms">
-  <Display>DocumentLibraryForm</Display>
-  <Edit>DocumentLibraryForm</Edit>
-  <New>DocumentLibraryForm</New>
-</FormTemplates>
-</file>
-
-<file path=customXml/item3.xml><?xml version="1.0" encoding="utf-8"?>
 <ct:contentTypeSchema xmlns:ct="http://schemas.microsoft.com/office/2006/metadata/contentType" xmlns:ma="http://schemas.microsoft.com/office/2006/metadata/properties/metaAttributes" ct:_="" ma:_="" ma:contentTypeName="Documento" ma:contentTypeID="0x01010001E48B58A68BE64E9120D347E3E06B3A" ma:contentTypeVersion="19" ma:contentTypeDescription="Crie um novo documento." ma:contentTypeScope="" ma:versionID="2f90046ec77328b7f86417d2e03b3d33">
   <xsd:schema xmlns:xsd="http://www.w3.org/2001/XMLSchema" xmlns:xs="http://www.w3.org/2001/XMLSchema" xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:ns2="851b35d3-0456-4d6a-bc2f-da927e91d158" xmlns:ns3="19483571-f922-4e8e-9c1c-26f0a2252132" targetNamespace="http://schemas.microsoft.com/office/2006/metadata/properties" ma:root="true" ma:fieldsID="c815006ac2d4f05ee97fdd57e40d8e38" ns2:_="" ns3:_="">
     <xsd:import namespace="851b35d3-0456-4d6a-bc2f-da927e91d158"/>
@@ -23745,26 +25644,27 @@
 </ct:contentTypeSchema>
 </file>
 
-<file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{FFD3D529-BCD3-4ECD-9B2A-42924892FFCB}">
-  <ds:schemaRefs>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/properties"/>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
-    <ds:schemaRef ds:uri="851b35d3-0456-4d6a-bc2f-da927e91d158"/>
-    <ds:schemaRef ds:uri="19483571-f922-4e8e-9c1c-26f0a2252132"/>
-  </ds:schemaRefs>
-</ds:datastoreItem>
+<file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
+<p:properties xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls">
+  <documentManagement>
+    <lcf76f155ced4ddcb4097134ff3c332f xmlns="851b35d3-0456-4d6a-bc2f-da927e91d158">
+      <Terms xmlns="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
+    </lcf76f155ced4ddcb4097134ff3c332f>
+    <TaxCatchAll xmlns="19483571-f922-4e8e-9c1c-26f0a2252132" xsi:nil="true"/>
+  </documentManagement>
+</p:properties>
 </file>
 
-<file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{E3B4D9D5-B351-46EB-A728-C3362FE437D4}">
-  <ds:schemaRefs>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms"/>
-  </ds:schemaRefs>
-</ds:datastoreItem>
+<file path=customXml/item3.xml><?xml version="1.0" encoding="utf-8"?>
+<?mso-contentType ?>
+<FormTemplates xmlns="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms">
+  <Display>DocumentLibraryForm</Display>
+  <Edit>DocumentLibraryForm</Edit>
+  <New>DocumentLibraryForm</New>
+</FormTemplates>
 </file>
 
-<file path=customXml/itemProps3.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
 <ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{32608D25-EC36-42FE-A1DC-F778995A6799}">
   <ds:schemaRefs>
     <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/contentType"/>
@@ -23783,6 +25683,25 @@
 </ds:datastoreItem>
 </file>
 
+<file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{FFD3D529-BCD3-4ECD-9B2A-42924892FFCB}">
+  <ds:schemaRefs>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/properties"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
+    <ds:schemaRef ds:uri="851b35d3-0456-4d6a-bc2f-da927e91d158"/>
+    <ds:schemaRef ds:uri="19483571-f922-4e8e-9c1c-26f0a2252132"/>
+  </ds:schemaRefs>
+</ds:datastoreItem>
+</file>
+
+<file path=customXml/itemProps3.xml><?xml version="1.0" encoding="utf-8"?>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{E3B4D9D5-B351-46EB-A728-C3362FE437D4}">
+  <ds:schemaRefs>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms"/>
+  </ds:schemaRefs>
+</ds:datastoreItem>
+</file>
+
 <file path=docMetadata/LabelInfo.xml><?xml version="1.0" encoding="utf-8"?>
 <clbl:labelList xmlns:clbl="http://schemas.microsoft.com/office/2020/mipLabelMetadata">
   <clbl:label id="{8fb9bcf5-18ab-4a9a-b2f8-fa184e71e6ca}" enabled="1" method="Privileged" siteId="{5b6f6241-9a57-4be4-8e50-1dfa72e79a57}" removed="0"/>
